--- a/saavu2.xlsx
+++ b/saavu2.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jayak\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/84c9e8aa81d5b49a/Desktop/weighted-kmeans-dc-location/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EDEFCC3-5858-4EEB-B772-77B8F6028255}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{B277FC28-4745-4223-8C79-53AD42E5289A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C9EB9C72-DFBB-4E87-BF8E-0C2A3DA7B62E}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6C2950A3-A5DC-4E1C-8EC9-030D30FBD1A4}"/>
   </bookViews>
@@ -36,15 +36,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="509" uniqueCount="509">
   <si>
-    <t>STORES</t>
-  </si>
-  <si>
-    <t>LAT</t>
-  </si>
-  <si>
-    <t>LONG</t>
-  </si>
-  <si>
     <t>sales</t>
   </si>
   <si>
@@ -1560,7 +1551,16 @@
     <t>DPI70316</t>
   </si>
   <si>
-    <t>weight</t>
+    <t>store</t>
+  </si>
+  <si>
+    <t>lat</t>
+  </si>
+  <si>
+    <t>long</t>
+  </si>
+  <si>
+    <t>demand_cft</t>
   </si>
 </sst>
 </file>
@@ -1581,12 +1581,18 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -1601,9 +1607,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1920,27 +1927,30 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE31FFBA-419D-4219-9079-000C88261140}">
   <dimension ref="A1:E505"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="5" max="5" width="16.109375" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>505</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>508</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B2">
         <v>10.025</v>
@@ -1952,13 +1962,12 @@
         <v>1391311.2400000007</v>
       </c>
       <c r="E2">
-        <f>D2/100000</f>
-        <v>13.913112400000006</v>
+        <v>41.297205439999999</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B3">
         <v>10.959</v>
@@ -1970,13 +1979,12 @@
         <v>1894015.4100000011</v>
       </c>
       <c r="E3">
-        <f t="shared" ref="E3:E66" si="0">D3/100000</f>
-        <v>18.940154100000012</v>
+        <v>55.879584799999989</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B4">
         <v>11.319000000000001</v>
@@ -1988,13 +1996,12 @@
         <v>806187.35499999986</v>
       </c>
       <c r="E4">
-        <f t="shared" si="0"/>
-        <v>8.0618735499999978</v>
+        <v>33.268048280000002</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B5">
         <v>13.009</v>
@@ -2006,13 +2013,12 @@
         <v>10000</v>
       </c>
       <c r="E5">
-        <f t="shared" si="0"/>
-        <v>0.1</v>
+        <v>93.988592240000003</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B6">
         <v>10.192</v>
@@ -2024,13 +2030,12 @@
         <v>1565861.1900000004</v>
       </c>
       <c r="E6">
-        <f t="shared" si="0"/>
-        <v>15.658611900000004</v>
+        <v>40.427373479999993</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B7">
         <v>12.843999999999999</v>
@@ -2042,13 +2047,12 @@
         <v>1159777.94</v>
       </c>
       <c r="E7">
-        <f t="shared" si="0"/>
-        <v>11.5977794</v>
+        <v>63.746647850000002</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B8">
         <v>13.346</v>
@@ -2060,13 +2064,12 @@
         <v>1963860.5700000008</v>
       </c>
       <c r="E8">
-        <f t="shared" si="0"/>
-        <v>19.638605700000006</v>
+        <v>86.276473920000001</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B9">
         <v>12.81</v>
@@ -2078,13 +2081,12 @@
         <v>2041918.8450000009</v>
       </c>
       <c r="E9">
-        <f t="shared" si="0"/>
-        <v>20.419188450000011</v>
+        <v>91.168501800000016</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B10">
         <v>8.5359999999999996</v>
@@ -2096,13 +2098,12 @@
         <v>2453649.6725000003</v>
       </c>
       <c r="E10">
-        <f t="shared" si="0"/>
-        <v>24.536496725000003</v>
+        <v>86.997666539999997</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B11">
         <v>8.1769999999999996</v>
@@ -2114,13 +2115,12 @@
         <v>2545405.430000002</v>
       </c>
       <c r="E11">
-        <f t="shared" si="0"/>
-        <v>25.454054300000021</v>
+        <v>82.871676070000007</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B12">
         <v>13.038</v>
@@ -2132,13 +2132,12 @@
         <v>2403857.600000001</v>
       </c>
       <c r="E12">
-        <f t="shared" si="0"/>
-        <v>24.03857600000001</v>
+        <v>113.41016794000001</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B13">
         <v>13.023999999999999</v>
@@ -2150,13 +2149,12 @@
         <v>1536303.2300000007</v>
       </c>
       <c r="E13">
-        <f t="shared" si="0"/>
-        <v>15.363032300000008</v>
+        <v>90.756860099999997</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B14">
         <v>13.157999999999999</v>
@@ -2168,13 +2166,12 @@
         <v>2889231.95</v>
       </c>
       <c r="E14">
-        <f t="shared" si="0"/>
-        <v>28.892319500000003</v>
+        <v>129.90572293999998</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B15">
         <v>9.3789999999999996</v>
@@ -2186,13 +2183,12 @@
         <v>1765869.2900000005</v>
       </c>
       <c r="E15">
-        <f t="shared" si="0"/>
-        <v>17.658692900000005</v>
+        <v>39.665742480000006</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B16">
         <v>11.868</v>
@@ -2204,13 +2200,12 @@
         <v>2286972.5860000006</v>
       </c>
       <c r="E16">
-        <f t="shared" si="0"/>
-        <v>22.869725860000006</v>
+        <v>76.755636049999993</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B17">
         <v>12.996</v>
@@ -2222,13 +2217,12 @@
         <v>1799592.3010000002</v>
       </c>
       <c r="E17">
-        <f t="shared" si="0"/>
-        <v>17.995923010000002</v>
+        <v>71.558893099999977</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B18">
         <v>13.945</v>
@@ -2240,13 +2234,12 @@
         <v>2780851.5100000026</v>
       </c>
       <c r="E18">
-        <f t="shared" si="0"/>
-        <v>27.808515100000026</v>
+        <v>112.80354775000001</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B19">
         <v>13.061</v>
@@ -2258,13 +2251,12 @@
         <v>2068389.7200000004</v>
       </c>
       <c r="E19">
-        <f t="shared" si="0"/>
-        <v>20.683897200000004</v>
+        <v>73.570742839999994</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B20">
         <v>10.792999999999999</v>
@@ -2276,13 +2268,12 @@
         <v>1578105.8200000003</v>
       </c>
       <c r="E20">
-        <f t="shared" si="0"/>
-        <v>15.781058200000002</v>
+        <v>48.187718400000009</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B21">
         <v>14.468999999999999</v>
@@ -2294,13 +2285,12 @@
         <v>1986991.5800000008</v>
       </c>
       <c r="E21">
-        <f t="shared" si="0"/>
-        <v>19.869915800000008</v>
+        <v>137.72677575</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B22">
         <v>14.411</v>
@@ -2312,13 +2302,12 @@
         <v>1634757.7200000002</v>
       </c>
       <c r="E22">
-        <f t="shared" si="0"/>
-        <v>16.347577200000003</v>
+        <v>61.964390130000012</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B23">
         <v>9.5</v>
@@ -2330,13 +2319,12 @@
         <v>1786987.540000001</v>
       </c>
       <c r="E23">
-        <f t="shared" si="0"/>
-        <v>17.869875400000009</v>
+        <v>57.011958059999998</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B24">
         <v>15.365</v>
@@ -2348,13 +2336,12 @@
         <v>1492480.91</v>
       </c>
       <c r="E24">
-        <f t="shared" si="0"/>
-        <v>14.924809099999999</v>
+        <v>75.034269940000001</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B25">
         <v>9.9770000000000003</v>
@@ -2366,13 +2353,12 @@
         <v>1668985.4400000002</v>
       </c>
       <c r="E25">
-        <f t="shared" si="0"/>
-        <v>16.689854400000002</v>
+        <v>45.991</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B26">
         <v>12.885</v>
@@ -2384,13 +2370,12 @@
         <v>1935476.2500000002</v>
       </c>
       <c r="E26">
-        <f t="shared" si="0"/>
-        <v>19.354762500000003</v>
+        <v>69.517077069999999</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B27">
         <v>13.087999999999999</v>
@@ -2402,13 +2387,12 @@
         <v>2539449.2085000011</v>
       </c>
       <c r="E27">
-        <f t="shared" si="0"/>
-        <v>25.39449208500001</v>
+        <v>118.63043666999999</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B28">
         <v>9.9450000000000003</v>
@@ -2420,13 +2404,12 @@
         <v>1574566.7599999998</v>
       </c>
       <c r="E28">
-        <f t="shared" si="0"/>
-        <v>15.745667599999997</v>
+        <v>39.056425590000003</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B29">
         <v>14.786</v>
@@ -2438,13 +2421,12 @@
         <v>1199871.2999999998</v>
       </c>
       <c r="E29">
-        <f t="shared" si="0"/>
-        <v>11.998712999999999</v>
+        <v>51.111506989999995</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B30">
         <v>9.9619999999999997</v>
@@ -2456,13 +2438,12 @@
         <v>2612049.2300000018</v>
       </c>
       <c r="E30">
-        <f t="shared" si="0"/>
-        <v>26.12049230000002</v>
+        <v>90.556615119999989</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B31">
         <v>13.131</v>
@@ -2474,13 +2455,12 @@
         <v>1729025.4400000009</v>
       </c>
       <c r="E31">
-        <f t="shared" si="0"/>
-        <v>17.290254400000009</v>
+        <v>80.491797360000007</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B32">
         <v>13.124000000000001</v>
@@ -2492,13 +2472,12 @@
         <v>3471794.1250000028</v>
       </c>
       <c r="E32">
-        <f t="shared" si="0"/>
-        <v>34.717941250000031</v>
+        <v>137.7462625</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B33">
         <v>9.9350000000000005</v>
@@ -2510,13 +2489,12 @@
         <v>2410134.0200000009</v>
       </c>
       <c r="E33">
-        <f t="shared" si="0"/>
-        <v>24.10134020000001</v>
+        <v>82.065612869999995</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B34">
         <v>14.512</v>
@@ -2528,13 +2506,12 @@
         <v>815045.94999999984</v>
       </c>
       <c r="E34">
-        <f t="shared" si="0"/>
-        <v>8.1504594999999984</v>
+        <v>40.914393320000002</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B35">
         <v>13.103999999999999</v>
@@ -2546,13 +2523,12 @@
         <v>1892125.7230000007</v>
       </c>
       <c r="E35">
-        <f t="shared" si="0"/>
-        <v>18.921257230000005</v>
+        <v>94.207473119999989</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B36">
         <v>8.5150000000000006</v>
@@ -2564,13 +2540,12 @@
         <v>2345239.3500000006</v>
       </c>
       <c r="E36">
-        <f t="shared" si="0"/>
-        <v>23.452393500000007</v>
+        <v>51.342081470000011</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B37">
         <v>15.348000000000001</v>
@@ -2582,13 +2557,12 @@
         <v>2138770.3050000006</v>
       </c>
       <c r="E37">
-        <f t="shared" si="0"/>
-        <v>21.387703050000006</v>
+        <v>89.43269527999999</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B38">
         <v>13.061999999999999</v>
@@ -2600,13 +2574,12 @@
         <v>1895595.6184999999</v>
       </c>
       <c r="E38">
-        <f t="shared" si="0"/>
-        <v>18.955956184999998</v>
+        <v>87.623532229999995</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B39">
         <v>10.016</v>
@@ -2618,13 +2591,12 @@
         <v>3454897.2850000039</v>
       </c>
       <c r="E39">
-        <f t="shared" si="0"/>
-        <v>34.548972850000041</v>
+        <v>113.62947596999999</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B40">
         <v>12.992000000000001</v>
@@ -2636,13 +2608,12 @@
         <v>2406394.6700000009</v>
       </c>
       <c r="E40">
-        <f t="shared" si="0"/>
-        <v>24.06394670000001</v>
+        <v>97.860420419999997</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B41">
         <v>15.464</v>
@@ -2654,13 +2625,12 @@
         <v>2110505.3745000008</v>
       </c>
       <c r="E41">
-        <f t="shared" si="0"/>
-        <v>21.10505374500001</v>
+        <v>120.70724465999999</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B42">
         <v>10.366</v>
@@ -2672,13 +2642,12 @@
         <v>1735908.4075000007</v>
       </c>
       <c r="E42">
-        <f t="shared" si="0"/>
-        <v>17.359084075000005</v>
+        <v>63.646055100000012</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B43">
         <v>15.257999999999999</v>
@@ -2690,13 +2659,12 @@
         <v>2362977.3940000013</v>
       </c>
       <c r="E43">
-        <f t="shared" si="0"/>
-        <v>23.629773940000014</v>
+        <v>79.885497510000008</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B44">
         <v>11.287000000000001</v>
@@ -2708,13 +2676,12 @@
         <v>1801111.0900000003</v>
       </c>
       <c r="E44">
-        <f t="shared" si="0"/>
-        <v>18.011110900000002</v>
+        <v>75.970188950000008</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B45">
         <v>13.066000000000001</v>
@@ -2726,13 +2693,12 @@
         <v>1520926.3200000005</v>
       </c>
       <c r="E45">
-        <f t="shared" si="0"/>
-        <v>15.209263200000006</v>
+        <v>58.831397229999993</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B46">
         <v>9.8960000000000008</v>
@@ -2744,13 +2710,12 @@
         <v>1148545.6100000001</v>
       </c>
       <c r="E46">
-        <f t="shared" si="0"/>
-        <v>11.4854561</v>
+        <v>24.03516849</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B47">
         <v>9.984</v>
@@ -2762,13 +2727,12 @@
         <v>846114.49000000022</v>
       </c>
       <c r="E47">
-        <f t="shared" si="0"/>
-        <v>8.4611449000000025</v>
+        <v>17.608908720000002</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B48">
         <v>12.965</v>
@@ -2780,13 +2744,12 @@
         <v>2107279.7950000004</v>
       </c>
       <c r="E48">
-        <f t="shared" si="0"/>
-        <v>21.072797950000005</v>
+        <v>82.637839190000008</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B49">
         <v>9.984</v>
@@ -2798,13 +2761,12 @@
         <v>2208678.120000001</v>
       </c>
       <c r="E49">
-        <f t="shared" si="0"/>
-        <v>22.086781200000011</v>
+        <v>56.299495159999992</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B50">
         <v>8.4819999999999993</v>
@@ -2816,13 +2778,12 @@
         <v>1582088.5600000003</v>
       </c>
       <c r="E50">
-        <f t="shared" si="0"/>
-        <v>15.820885600000002</v>
+        <v>47.273919109999994</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B51">
         <v>13.355</v>
@@ -2834,13 +2795,12 @@
         <v>1596611.1940000004</v>
       </c>
       <c r="E51">
-        <f t="shared" si="0"/>
-        <v>15.966111940000003</v>
+        <v>55.125807519999995</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B52">
         <v>15.545</v>
@@ -2852,13 +2812,12 @@
         <v>1704246.3400000003</v>
       </c>
       <c r="E52">
-        <f t="shared" si="0"/>
-        <v>17.042463400000003</v>
+        <v>70.259593580000001</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B53">
         <v>12.686</v>
@@ -2870,13 +2829,12 @@
         <v>1860230.5150000008</v>
       </c>
       <c r="E53">
-        <f t="shared" si="0"/>
-        <v>18.60230515000001</v>
+        <v>62.591550269999985</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B54">
         <v>14.808</v>
@@ -2888,13 +2846,12 @@
         <v>1827854.7500000009</v>
       </c>
       <c r="E54">
-        <f t="shared" si="0"/>
-        <v>18.278547500000009</v>
+        <v>78.946161259999982</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B55">
         <v>13.135999999999999</v>
@@ -2906,13 +2863,12 @@
         <v>2463968.0200000005</v>
       </c>
       <c r="E55">
-        <f t="shared" si="0"/>
-        <v>24.639680200000004</v>
+        <v>101.76988238000001</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B56">
         <v>8.5299999999999994</v>
@@ -2924,13 +2880,12 @@
         <v>1362876</v>
       </c>
       <c r="E56">
-        <f t="shared" si="0"/>
-        <v>13.62876</v>
+        <v>44.190959890000002</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B57">
         <v>8.8040000000000003</v>
@@ -2942,13 +2897,12 @@
         <v>2549014.3900000011</v>
       </c>
       <c r="E57">
-        <f t="shared" si="0"/>
-        <v>25.49014390000001</v>
+        <v>93.804589360000008</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B58">
         <v>15.731999999999999</v>
@@ -2959,14 +2913,13 @@
       <c r="D58">
         <v>1227601.5199999998</v>
       </c>
-      <c r="E58">
-        <f t="shared" si="0"/>
-        <v>12.276015199999998</v>
+      <c r="E58" s="2">
+        <v>49.104060799999992</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B59">
         <v>13.192</v>
@@ -2978,13 +2931,12 @@
         <v>2226948.3650000012</v>
       </c>
       <c r="E59">
-        <f t="shared" si="0"/>
-        <v>22.269483650000012</v>
+        <v>99.072804739999995</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B60">
         <v>13.073</v>
@@ -2996,13 +2948,12 @@
         <v>1558090.3500000006</v>
       </c>
       <c r="E60">
-        <f t="shared" si="0"/>
-        <v>15.580903500000005</v>
+        <v>69.661814950000007</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B61">
         <v>15.525</v>
@@ -3014,13 +2965,12 @@
         <v>3817390.8175000031</v>
       </c>
       <c r="E61">
-        <f t="shared" si="0"/>
-        <v>38.17390817500003</v>
+        <v>157.49350527000001</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B62">
         <v>12.981999999999999</v>
@@ -3032,13 +2982,12 @@
         <v>2090753.0300000007</v>
       </c>
       <c r="E62">
-        <f t="shared" si="0"/>
-        <v>20.907530300000008</v>
+        <v>69.614203040000007</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B63">
         <v>9.9440000000000008</v>
@@ -3050,13 +2999,12 @@
         <v>1041427.8600000001</v>
       </c>
       <c r="E63">
-        <f t="shared" si="0"/>
-        <v>10.414278600000001</v>
+        <v>15.036999999999999</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B64">
         <v>13.346</v>
@@ -3068,13 +3016,12 @@
         <v>930633.13000000012</v>
       </c>
       <c r="E64">
-        <f t="shared" si="0"/>
-        <v>9.3063313000000019</v>
+        <v>33.561415999999994</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B65">
         <v>15.273999999999999</v>
@@ -3086,13 +3033,12 @@
         <v>3196145.850000002</v>
       </c>
       <c r="E65">
-        <f t="shared" si="0"/>
-        <v>31.96145850000002</v>
+        <v>122.2742197</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B66">
         <v>12.858000000000001</v>
@@ -3104,13 +3050,12 @@
         <v>890859.57</v>
       </c>
       <c r="E66">
-        <f t="shared" si="0"/>
-        <v>8.9085956999999993</v>
+        <v>29.316899039999999</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B67">
         <v>12.955</v>
@@ -3122,13 +3067,12 @@
         <v>1474320.7779999999</v>
       </c>
       <c r="E67">
-        <f t="shared" ref="E67:E130" si="1">D67/100000</f>
-        <v>14.743207779999999</v>
+        <v>24.084488960000002</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B68">
         <v>14.62</v>
@@ -3140,13 +3084,12 @@
         <v>1154042.0000000002</v>
       </c>
       <c r="E68">
-        <f t="shared" si="1"/>
-        <v>11.540420000000003</v>
+        <v>59.569198480000004</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B69">
         <v>11.754</v>
@@ -3158,13 +3101,12 @@
         <v>1514679.93</v>
       </c>
       <c r="E69">
-        <f t="shared" si="1"/>
-        <v>15.1467993</v>
+        <v>61.173617569999998</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B70">
         <v>13.058999999999999</v>
@@ -3176,13 +3118,12 @@
         <v>1339391.9700000002</v>
       </c>
       <c r="E70">
-        <f t="shared" si="1"/>
-        <v>13.393919700000001</v>
+        <v>45.193988989999994</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B71">
         <v>15.731999999999999</v>
@@ -3193,14 +3134,13 @@
       <c r="D71">
         <v>214758.73</v>
       </c>
-      <c r="E71">
-        <f t="shared" si="1"/>
-        <v>2.1475873000000001</v>
+      <c r="E71" s="2">
+        <v>8.5903492000000004</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B72">
         <v>12.984999999999999</v>
@@ -3212,13 +3152,12 @@
         <v>1656171.6850000001</v>
       </c>
       <c r="E72">
-        <f t="shared" si="1"/>
-        <v>16.56171685</v>
+        <v>77.607055839999987</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B73">
         <v>9.4570000000000007</v>
@@ -3230,13 +3169,12 @@
         <v>1372180.2999999998</v>
       </c>
       <c r="E73">
-        <f t="shared" si="1"/>
-        <v>13.721802999999998</v>
+        <v>27.845229359999998</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B74">
         <v>13.007999999999999</v>
@@ -3248,13 +3186,12 @@
         <v>3010965.3458000016</v>
       </c>
       <c r="E74">
-        <f t="shared" si="1"/>
-        <v>30.109653458000018</v>
+        <v>121.24150382000001</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B75">
         <v>15.492000000000001</v>
@@ -3266,13 +3203,12 @@
         <v>2401400.6600000011</v>
       </c>
       <c r="E75">
-        <f t="shared" si="1"/>
-        <v>24.014006600000013</v>
+        <v>109.77473927</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B76">
         <v>8.8659999999999997</v>
@@ -3284,13 +3220,12 @@
         <v>952431.26000000013</v>
       </c>
       <c r="E76">
-        <f t="shared" si="1"/>
-        <v>9.5243126000000018</v>
+        <v>27.960246769999998</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B77">
         <v>15.608000000000001</v>
@@ -3302,13 +3237,12 @@
         <v>2932250.8775000013</v>
       </c>
       <c r="E77">
-        <f t="shared" si="1"/>
-        <v>29.322508775000014</v>
+        <v>127.09983191999997</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B78">
         <v>10.377000000000001</v>
@@ -3320,13 +3254,12 @@
         <v>1126902.32</v>
       </c>
       <c r="E78">
-        <f t="shared" si="1"/>
-        <v>11.269023200000001</v>
+        <v>40.975594719999997</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B79">
         <v>10.079000000000001</v>
@@ -3338,13 +3271,12 @@
         <v>1700685.398000001</v>
       </c>
       <c r="E79">
-        <f t="shared" si="1"/>
-        <v>17.00685398000001</v>
+        <v>55.951363359999995</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B80">
         <v>13.135</v>
@@ -3356,13 +3288,12 @@
         <v>2135061.1300000008</v>
       </c>
       <c r="E80">
-        <f t="shared" si="1"/>
-        <v>21.350611300000008</v>
+        <v>99.956875119999992</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B81">
         <v>13.045</v>
@@ -3374,13 +3305,12 @@
         <v>3295031.4015000034</v>
       </c>
       <c r="E81">
-        <f t="shared" si="1"/>
-        <v>32.950314015000032</v>
+        <v>171.25894001999995</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B82">
         <v>13.005000000000001</v>
@@ -3392,13 +3322,12 @@
         <v>2353874.4000000008</v>
       </c>
       <c r="E82">
-        <f t="shared" si="1"/>
-        <v>23.538744000000008</v>
+        <v>108.25222512999999</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B83">
         <v>15.542</v>
@@ -3410,13 +3339,12 @@
         <v>3869218.7300000032</v>
       </c>
       <c r="E83">
-        <f t="shared" si="1"/>
-        <v>38.692187300000029</v>
+        <v>152.37332232</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B84">
         <v>15.499000000000001</v>
@@ -3428,13 +3356,12 @@
         <v>3059781.1210000021</v>
       </c>
       <c r="E84">
-        <f t="shared" si="1"/>
-        <v>30.597811210000021</v>
+        <v>137.64539505000002</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B85">
         <v>15.284000000000001</v>
@@ -3446,13 +3373,12 @@
         <v>2800092.3450000025</v>
       </c>
       <c r="E85">
-        <f t="shared" si="1"/>
-        <v>28.000923450000027</v>
+        <v>98.886500380000001</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B86">
         <v>13.034000000000001</v>
@@ -3464,13 +3390,12 @@
         <v>4186897.3400000031</v>
       </c>
       <c r="E86">
-        <f t="shared" si="1"/>
-        <v>41.86897340000003</v>
+        <v>174.43258148999996</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B87">
         <v>12.871</v>
@@ -3482,13 +3407,12 @@
         <v>3134395.6100000013</v>
       </c>
       <c r="E87">
-        <f t="shared" si="1"/>
-        <v>31.343956100000014</v>
+        <v>131.72022438000002</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B88">
         <v>13.347</v>
@@ -3500,13 +3424,12 @@
         <v>3023221.9600000028</v>
       </c>
       <c r="E88">
-        <f t="shared" si="1"/>
-        <v>30.232219600000029</v>
+        <v>128.67002751999999</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B89">
         <v>13.085000000000001</v>
@@ -3518,13 +3441,12 @@
         <v>3695866.8900000015</v>
       </c>
       <c r="E89">
-        <f t="shared" si="1"/>
-        <v>36.958668900000013</v>
+        <v>151.83197394000001</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B90">
         <v>13.053000000000001</v>
@@ -3536,13 +3458,12 @@
         <v>1786667.5680000002</v>
       </c>
       <c r="E90">
-        <f t="shared" si="1"/>
-        <v>17.866675680000004</v>
+        <v>70.438586980000025</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B91">
         <v>12.973000000000001</v>
@@ -3554,13 +3475,12 @@
         <v>3627985.8925000024</v>
       </c>
       <c r="E91">
-        <f t="shared" si="1"/>
-        <v>36.279858925000021</v>
+        <v>165.86665209</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B92">
         <v>15.584</v>
@@ -3572,13 +3492,12 @@
         <v>3943833.5000000037</v>
       </c>
       <c r="E92">
-        <f t="shared" si="1"/>
-        <v>39.438335000000038</v>
+        <v>160.79441849999998</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B93">
         <v>15.526999999999999</v>
@@ -3590,13 +3509,12 @@
         <v>2606742.2300000023</v>
       </c>
       <c r="E93">
-        <f t="shared" si="1"/>
-        <v>26.067422300000022</v>
+        <v>114.30460316</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B94">
         <v>13.035</v>
@@ -3608,13 +3526,12 @@
         <v>1895208.7375000005</v>
       </c>
       <c r="E94">
-        <f t="shared" si="1"/>
-        <v>18.952087375000005</v>
+        <v>27.65862036</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B95">
         <v>15.557</v>
@@ -3626,13 +3543,12 @@
         <v>2304318.7080000006</v>
       </c>
       <c r="E95">
-        <f t="shared" si="1"/>
-        <v>23.043187080000006</v>
+        <v>107.20581291000001</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B96">
         <v>13.08</v>
@@ -3644,13 +3560,12 @@
         <v>3059530.7320000022</v>
       </c>
       <c r="E96">
-        <f t="shared" si="1"/>
-        <v>30.595307320000021</v>
+        <v>132.81126806</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B97">
         <v>13.08</v>
@@ -3662,13 +3577,12 @@
         <v>2527912.6700000023</v>
       </c>
       <c r="E97">
-        <f t="shared" si="1"/>
-        <v>25.279126700000024</v>
+        <v>151.87199567000002</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B98">
         <v>13.045999999999999</v>
@@ -3680,13 +3594,12 @@
         <v>2551333.9275000012</v>
       </c>
       <c r="E98">
-        <f t="shared" si="1"/>
-        <v>25.513339275000011</v>
+        <v>97.519304879999993</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B99">
         <v>9.9610000000000003</v>
@@ -3698,13 +3611,12 @@
         <v>2689641.1900000009</v>
       </c>
       <c r="E99">
-        <f t="shared" si="1"/>
-        <v>26.896411900000007</v>
+        <v>62.686835119999998</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B100">
         <v>13.116</v>
@@ -3716,13 +3628,12 @@
         <v>3196226.8130000019</v>
       </c>
       <c r="E100">
-        <f t="shared" si="1"/>
-        <v>31.96226813000002</v>
+        <v>164.09465016000001</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B101">
         <v>13.032</v>
@@ -3734,13 +3645,12 @@
         <v>2972033.6830000025</v>
       </c>
       <c r="E101">
-        <f t="shared" si="1"/>
-        <v>29.720336830000026</v>
+        <v>115.75139107999999</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B102">
         <v>12.922000000000001</v>
@@ -3752,13 +3662,12 @@
         <v>3600055.5717000011</v>
       </c>
       <c r="E102">
-        <f t="shared" si="1"/>
-        <v>36.000555717000012</v>
+        <v>112.73454219</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B103">
         <v>12.927</v>
@@ -3770,13 +3679,12 @@
         <v>3509680.773000001</v>
       </c>
       <c r="E103">
-        <f t="shared" si="1"/>
-        <v>35.096807730000009</v>
+        <v>165.16716377</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B104">
         <v>12.942</v>
@@ -3788,13 +3696,12 @@
         <v>3675548.5600000028</v>
       </c>
       <c r="E104">
-        <f t="shared" si="1"/>
-        <v>36.755485600000029</v>
+        <v>98.303539369999982</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="B105">
         <v>11.257999999999999</v>
@@ -3806,13 +3713,12 @@
         <v>1943253.9620000012</v>
       </c>
       <c r="E105">
-        <f t="shared" si="1"/>
-        <v>19.432539620000011</v>
+        <v>64.328117490000011</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B106">
         <v>9.9309999999999992</v>
@@ -3824,13 +3730,12 @@
         <v>3837838.2500000028</v>
       </c>
       <c r="E106">
-        <f t="shared" si="1"/>
-        <v>38.378382500000029</v>
+        <v>143.1621979</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B107">
         <v>8.5120000000000005</v>
@@ -3842,13 +3747,12 @@
         <v>2088559.4500000004</v>
       </c>
       <c r="E107">
-        <f t="shared" si="1"/>
-        <v>20.885594500000003</v>
+        <v>62.721587420000006</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B108">
         <v>10.003</v>
@@ -3860,13 +3764,12 @@
         <v>3078630.0000000019</v>
       </c>
       <c r="E108">
-        <f t="shared" si="1"/>
-        <v>30.786300000000018</v>
+        <v>135.79601133</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B109">
         <v>13.013999999999999</v>
@@ -3878,13 +3781,12 @@
         <v>1992045.4420000007</v>
       </c>
       <c r="E109">
-        <f t="shared" si="1"/>
-        <v>19.920454420000006</v>
+        <v>67.784533879999998</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B110">
         <v>12.875</v>
@@ -3896,13 +3798,12 @@
         <v>2896037.5160000017</v>
       </c>
       <c r="E110">
-        <f t="shared" si="1"/>
-        <v>28.960375160000016</v>
+        <v>135.40894881</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B111">
         <v>13.026999999999999</v>
@@ -3914,13 +3815,12 @@
         <v>2613216.2735000015</v>
       </c>
       <c r="E111">
-        <f t="shared" si="1"/>
-        <v>26.132162735000016</v>
+        <v>134.30264618000001</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B112">
         <v>12.957000000000001</v>
@@ -3932,13 +3832,12 @@
         <v>2714550.080000001</v>
       </c>
       <c r="E112">
-        <f t="shared" si="1"/>
-        <v>27.145500800000011</v>
+        <v>107.39169483000001</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B113">
         <v>12.936</v>
@@ -3950,13 +3849,12 @@
         <v>2132839.1200000006</v>
       </c>
       <c r="E113">
-        <f t="shared" si="1"/>
-        <v>21.328391200000006</v>
+        <v>92.21966651000001</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B114">
         <v>10.234999999999999</v>
@@ -3968,13 +3866,12 @@
         <v>1819889.9300000002</v>
       </c>
       <c r="E114">
-        <f t="shared" si="1"/>
-        <v>18.198899300000001</v>
+        <v>46.659428160000004</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B115">
         <v>10.523</v>
@@ -3986,13 +3883,12 @@
         <v>1924593.4900000009</v>
       </c>
       <c r="E115">
-        <f t="shared" si="1"/>
-        <v>19.245934900000009</v>
+        <v>61.253137890000005</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B116">
         <v>12.917</v>
@@ -4004,13 +3900,12 @@
         <v>2651898.1720000007</v>
       </c>
       <c r="E116">
-        <f t="shared" si="1"/>
-        <v>26.518981720000006</v>
+        <v>95.795220479999983</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B117">
         <v>15.459</v>
@@ -4022,13 +3917,12 @@
         <v>2908582.5700000022</v>
       </c>
       <c r="E117">
-        <f t="shared" si="1"/>
-        <v>29.085825700000022</v>
+        <v>131.44885389999999</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B118">
         <v>13.07</v>
@@ -4040,13 +3934,12 @@
         <v>3391717.6025000024</v>
       </c>
       <c r="E118">
-        <f t="shared" si="1"/>
-        <v>33.917176025000025</v>
+        <v>139.22461154999999</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="B119">
         <v>8.5289999999999999</v>
@@ -4058,13 +3951,12 @@
         <v>2203596.0300000012</v>
       </c>
       <c r="E119">
-        <f t="shared" si="1"/>
-        <v>22.035960300000013</v>
+        <v>69.877246439999993</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B120">
         <v>12.872</v>
@@ -4076,13 +3968,12 @@
         <v>1089481.6300000006</v>
       </c>
       <c r="E120">
-        <f t="shared" si="1"/>
-        <v>10.894816300000006</v>
+        <v>26.295348090000005</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B121">
         <v>13.122999999999999</v>
@@ -4094,13 +3985,12 @@
         <v>3675797.3605000032</v>
       </c>
       <c r="E121">
-        <f t="shared" si="1"/>
-        <v>36.757973605000032</v>
+        <v>124.64185642999999</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B122">
         <v>13.022</v>
@@ -4112,13 +4002,12 @@
         <v>1583080.2650000004</v>
       </c>
       <c r="E122">
-        <f t="shared" si="1"/>
-        <v>15.830802650000004</v>
+        <v>67.213288750000004</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B123">
         <v>15.35</v>
@@ -4130,13 +4019,12 @@
         <v>2483067.1570000011</v>
       </c>
       <c r="E123">
-        <f t="shared" si="1"/>
-        <v>24.83067157000001</v>
+        <v>104.41013482999999</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B124">
         <v>12.992000000000001</v>
@@ -4148,13 +4036,12 @@
         <v>2419685.3000000012</v>
       </c>
       <c r="E124">
-        <f t="shared" si="1"/>
-        <v>24.196853000000011</v>
+        <v>55.170393020000006</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B125">
         <v>12.926</v>
@@ -4166,13 +4053,12 @@
         <v>3597456.2150000022</v>
       </c>
       <c r="E125">
-        <f t="shared" si="1"/>
-        <v>35.974562150000018</v>
+        <v>156.16160591000002</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B126">
         <v>12.851000000000001</v>
@@ -4184,13 +4070,12 @@
         <v>1881257.0600000015</v>
       </c>
       <c r="E126">
-        <f t="shared" si="1"/>
-        <v>18.812570600000015</v>
+        <v>86.216208500000022</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B127">
         <v>13.063000000000001</v>
@@ -4202,13 +4087,12 @@
         <v>1915857.5100000007</v>
       </c>
       <c r="E127">
-        <f t="shared" si="1"/>
-        <v>19.158575100000007</v>
+        <v>71.97972833</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B128">
         <v>12.983000000000001</v>
@@ -4220,13 +4104,12 @@
         <v>2959023.7080000024</v>
       </c>
       <c r="E128">
-        <f t="shared" si="1"/>
-        <v>29.590237080000023</v>
+        <v>116.03335498</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B129">
         <v>13.048999999999999</v>
@@ -4238,13 +4121,12 @@
         <v>2536827.5650000018</v>
       </c>
       <c r="E129">
-        <f t="shared" si="1"/>
-        <v>25.368275650000019</v>
+        <v>87.048573290000007</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B130">
         <v>13.041</v>
@@ -4256,13 +4138,12 @@
         <v>3133921.4200000032</v>
       </c>
       <c r="E130">
-        <f t="shared" si="1"/>
-        <v>31.339214200000033</v>
+        <v>141.72703296</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B131">
         <v>11.935</v>
@@ -4274,13 +4155,12 @@
         <v>3848624.0025000027</v>
       </c>
       <c r="E131">
-        <f t="shared" ref="E131:E194" si="2">D131/100000</f>
-        <v>38.486240025000029</v>
+        <v>145.58214742000001</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B132">
         <v>15.882999999999999</v>
@@ -4292,13 +4172,12 @@
         <v>3305477.7150000022</v>
       </c>
       <c r="E132">
-        <f t="shared" si="2"/>
-        <v>33.054777150000021</v>
+        <v>148.1403535</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B133">
         <v>9.9629999999999992</v>
@@ -4310,13 +4189,12 @@
         <v>2152122.5600000005</v>
       </c>
       <c r="E133">
-        <f t="shared" si="2"/>
-        <v>21.521225600000005</v>
+        <v>39.359758620000008</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="B134">
         <v>13.047000000000001</v>
@@ -4328,13 +4206,12 @@
         <v>2754300.6300000027</v>
       </c>
       <c r="E134">
-        <f t="shared" si="2"/>
-        <v>27.543006300000027</v>
+        <v>121.18436645999998</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B135">
         <v>14.455</v>
@@ -4346,13 +4223,12 @@
         <v>3389548.4430000004</v>
       </c>
       <c r="E135">
-        <f t="shared" si="2"/>
-        <v>33.895484430000003</v>
+        <v>174.54029804999999</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="B136">
         <v>15.39</v>
@@ -4364,13 +4240,12 @@
         <v>2031568.3625000007</v>
       </c>
       <c r="E136">
-        <f t="shared" si="2"/>
-        <v>20.315683625000009</v>
+        <v>71.223442470000009</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="B137">
         <v>15.398999999999999</v>
@@ -4382,13 +4257,12 @@
         <v>2046548.4175000004</v>
       </c>
       <c r="E137">
-        <f t="shared" si="2"/>
-        <v>20.465484175000004</v>
+        <v>86.916462999999993</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B138">
         <v>12.99</v>
@@ -4400,13 +4274,12 @@
         <v>2774184.3495000028</v>
       </c>
       <c r="E138">
-        <f t="shared" si="2"/>
-        <v>27.74184349500003</v>
+        <v>113.58351808</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B139">
         <v>12.972</v>
@@ -4418,13 +4291,12 @@
         <v>3624847.4725000029</v>
       </c>
       <c r="E139">
-        <f t="shared" si="2"/>
-        <v>36.24847472500003</v>
+        <v>130.82707128000001</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B140">
         <v>10.026</v>
@@ -4436,13 +4308,12 @@
         <v>2881181.2199999997</v>
       </c>
       <c r="E140">
-        <f t="shared" si="2"/>
-        <v>28.811812199999999</v>
+        <v>83.839906690000007</v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="B141">
         <v>13.068</v>
@@ -4454,13 +4325,12 @@
         <v>2403177.404000001</v>
       </c>
       <c r="E141">
-        <f t="shared" si="2"/>
-        <v>24.031774040000009</v>
+        <v>66.932234889999989</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="B142">
         <v>14.448</v>
@@ -4472,13 +4342,12 @@
         <v>2195367.3100000005</v>
       </c>
       <c r="E142">
-        <f t="shared" si="2"/>
-        <v>21.953673100000007</v>
+        <v>94.849385789999999</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B143">
         <v>12.797000000000001</v>
@@ -4490,13 +4359,12 @@
         <v>3347237.5600000024</v>
       </c>
       <c r="E143">
-        <f t="shared" si="2"/>
-        <v>33.472375600000021</v>
+        <v>145.91838293000001</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="B144">
         <v>12.834</v>
@@ -4508,13 +4376,12 @@
         <v>2846202.5450000018</v>
       </c>
       <c r="E144">
-        <f t="shared" si="2"/>
-        <v>28.462025450000016</v>
+        <v>148.16292627999999</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="B145">
         <v>10.528</v>
@@ -4526,13 +4393,12 @@
         <v>2198959.5100000007</v>
       </c>
       <c r="E145">
-        <f t="shared" si="2"/>
-        <v>21.989595100000006</v>
+        <v>22.038991809999999</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B146">
         <v>15.367000000000001</v>
@@ -4544,13 +4410,12 @@
         <v>3064953.3550000018</v>
       </c>
       <c r="E146">
-        <f t="shared" si="2"/>
-        <v>30.649533550000019</v>
+        <v>169.43078549000001</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="B147">
         <v>12.939</v>
@@ -4562,13 +4427,12 @@
         <v>3140564.8640000019</v>
       </c>
       <c r="E147">
-        <f t="shared" si="2"/>
-        <v>31.40564864000002</v>
+        <v>115.96496099000001</v>
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="B148">
         <v>13.045</v>
@@ -4580,13 +4444,12 @@
         <v>2307777.0767000015</v>
       </c>
       <c r="E148">
-        <f t="shared" si="2"/>
-        <v>23.077770767000015</v>
+        <v>97.548270519999988</v>
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="B149">
         <v>13.124000000000001</v>
@@ -4598,13 +4461,12 @@
         <v>3378485.9725000006</v>
       </c>
       <c r="E149">
-        <f t="shared" si="2"/>
-        <v>33.784859725000004</v>
+        <v>171.24941355999999</v>
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B150">
         <v>12.797000000000001</v>
@@ -4616,13 +4478,12 @@
         <v>1857598.0700000005</v>
       </c>
       <c r="E150">
-        <f t="shared" si="2"/>
-        <v>18.575980700000006</v>
+        <v>79.483373470000004</v>
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="B151">
         <v>10.113</v>
@@ -4634,13 +4495,12 @@
         <v>1685171.5800000005</v>
       </c>
       <c r="E151">
-        <f t="shared" si="2"/>
-        <v>16.851715800000004</v>
+        <v>21.389574570000004</v>
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B152">
         <v>8.8780000000000001</v>
@@ -4652,13 +4512,12 @@
         <v>1831847.7700000007</v>
       </c>
       <c r="E152">
-        <f t="shared" si="2"/>
-        <v>18.318477700000006</v>
+        <v>56.001263080000001</v>
       </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B153">
         <v>12.958</v>
@@ -4670,13 +4529,12 @@
         <v>3265541.4520000019</v>
       </c>
       <c r="E153">
-        <f t="shared" si="2"/>
-        <v>32.655414520000022</v>
+        <v>116.54724108999999</v>
       </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B154">
         <v>15.448</v>
@@ -4688,13 +4546,12 @@
         <v>2790359.2700000019</v>
       </c>
       <c r="E154">
-        <f t="shared" si="2"/>
-        <v>27.903592700000019</v>
+        <v>136.56314483</v>
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B155">
         <v>12.913</v>
@@ -4706,13 +4563,12 @@
         <v>2720174.5050000018</v>
       </c>
       <c r="E155">
-        <f t="shared" si="2"/>
-        <v>27.201745050000017</v>
+        <v>132.34473268999997</v>
       </c>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B156">
         <v>13.018000000000001</v>
@@ -4724,13 +4580,12 @@
         <v>2913683.5500000012</v>
       </c>
       <c r="E156">
-        <f t="shared" si="2"/>
-        <v>29.136835500000011</v>
+        <v>127.67648194999998</v>
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B157">
         <v>8.4930000000000003</v>
@@ -4742,13 +4597,12 @@
         <v>2633189.9100000015</v>
       </c>
       <c r="E157">
-        <f t="shared" si="2"/>
-        <v>26.331899100000015</v>
+        <v>101.97064253000001</v>
       </c>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="B158">
         <v>11.247999999999999</v>
@@ -4760,13 +4614,12 @@
         <v>1741243.5100000007</v>
       </c>
       <c r="E158">
-        <f t="shared" si="2"/>
-        <v>17.412435100000007</v>
+        <v>64.406662200000014</v>
       </c>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B159">
         <v>13.11</v>
@@ -4778,13 +4631,12 @@
         <v>3134132.5405000001</v>
       </c>
       <c r="E159">
-        <f t="shared" si="2"/>
-        <v>31.341325405000003</v>
+        <v>133.79668708</v>
       </c>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="B160">
         <v>12.896000000000001</v>
@@ -4796,13 +4648,12 @@
         <v>2934563.6383000021</v>
       </c>
       <c r="E160">
-        <f t="shared" si="2"/>
-        <v>29.34563638300002</v>
+        <v>138.15013296000001</v>
       </c>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="B161">
         <v>13.042999999999999</v>
@@ -4814,13 +4665,12 @@
         <v>3759281.9400000041</v>
       </c>
       <c r="E161">
-        <f t="shared" si="2"/>
-        <v>37.592819400000039</v>
+        <v>150.50007586000004</v>
       </c>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B162">
         <v>13.1</v>
@@ -4832,13 +4682,12 @@
         <v>2021242.3800000008</v>
       </c>
       <c r="E162">
-        <f t="shared" si="2"/>
-        <v>20.212423800000007</v>
+        <v>93.606514959999998</v>
       </c>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="B163">
         <v>11.932</v>
@@ -4850,13 +4699,12 @@
         <v>3569096.2260000021</v>
       </c>
       <c r="E163">
-        <f t="shared" si="2"/>
-        <v>35.69096226000002</v>
+        <v>129.31327658000001</v>
       </c>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="B164">
         <v>8.73</v>
@@ -4868,13 +4716,12 @@
         <v>2907652.8100000019</v>
       </c>
       <c r="E164">
-        <f t="shared" si="2"/>
-        <v>29.076528100000019</v>
+        <v>106.88348563</v>
       </c>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="B165">
         <v>10.548999999999999</v>
@@ -4886,13 +4733,12 @@
         <v>1066794.5900000003</v>
       </c>
       <c r="E165">
-        <f t="shared" si="2"/>
-        <v>10.667945900000003</v>
+        <v>42.431447760000005</v>
       </c>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B166">
         <v>10.784000000000001</v>
@@ -4904,13 +4750,12 @@
         <v>2099097.7800000012</v>
       </c>
       <c r="E166">
-        <f t="shared" si="2"/>
-        <v>20.99097780000001</v>
+        <v>60.792930230000003</v>
       </c>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B167">
         <v>13.103999999999999</v>
@@ -4922,13 +4767,12 @@
         <v>2387985.3190000015</v>
       </c>
       <c r="E167">
-        <f t="shared" si="2"/>
-        <v>23.879853190000016</v>
+        <v>77.592704480000009</v>
       </c>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B168">
         <v>15.263999999999999</v>
@@ -4940,13 +4784,12 @@
         <v>2957249.0900000012</v>
       </c>
       <c r="E168">
-        <f t="shared" si="2"/>
-        <v>29.572490900000012</v>
+        <v>53.785477999999998</v>
       </c>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="B169">
         <v>15.836</v>
@@ -4958,13 +4801,12 @@
         <v>3032667.9279000019</v>
       </c>
       <c r="E169">
-        <f t="shared" si="2"/>
-        <v>30.326679279000018</v>
+        <v>145.01252209999998</v>
       </c>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="B170">
         <v>12.831</v>
@@ -4976,13 +4818,12 @@
         <v>3053703.8510000012</v>
       </c>
       <c r="E170">
-        <f t="shared" si="2"/>
-        <v>30.537038510000013</v>
+        <v>134.76338508999999</v>
       </c>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="B171">
         <v>9.5879999999999992</v>
@@ -4994,13 +4835,12 @@
         <v>1856441.5600000008</v>
       </c>
       <c r="E171">
-        <f t="shared" si="2"/>
-        <v>18.564415600000007</v>
+        <v>34.090603559999998</v>
       </c>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="B172">
         <v>13.066000000000001</v>
@@ -5012,13 +4852,12 @@
         <v>2023551.7600000007</v>
       </c>
       <c r="E172">
-        <f t="shared" si="2"/>
-        <v>20.235517600000009</v>
+        <v>103.95516875999999</v>
       </c>
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B173">
         <v>13.119</v>
@@ -5030,13 +4869,12 @@
         <v>2853768.4900000016</v>
       </c>
       <c r="E173">
-        <f t="shared" si="2"/>
-        <v>28.537684900000016</v>
+        <v>129.96221128000002</v>
       </c>
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="B174">
         <v>12.871</v>
@@ -5048,13 +4886,12 @@
         <v>2489524.2410000013</v>
       </c>
       <c r="E174">
-        <f t="shared" si="2"/>
-        <v>24.895242410000012</v>
+        <v>123.25258422000002</v>
       </c>
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="B175">
         <v>15.625999999999999</v>
@@ -5066,13 +4903,12 @@
         <v>3286898.1500000036</v>
       </c>
       <c r="E175">
-        <f t="shared" si="2"/>
-        <v>32.868981500000039</v>
+        <v>114.24801220000001</v>
       </c>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="B176">
         <v>13.93</v>
@@ -5084,13 +4920,12 @@
         <v>3312040.1550000012</v>
       </c>
       <c r="E176">
-        <f t="shared" si="2"/>
-        <v>33.120401550000011</v>
+        <v>148.70392756999999</v>
       </c>
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="B177">
         <v>9.92</v>
@@ -5102,13 +4937,12 @@
         <v>4732376.3825000012</v>
       </c>
       <c r="E177">
-        <f t="shared" si="2"/>
-        <v>47.323763825000015</v>
+        <v>164.48669544000001</v>
       </c>
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="B178">
         <v>10.032999999999999</v>
@@ -5120,13 +4954,12 @@
         <v>3354941.7900000028</v>
       </c>
       <c r="E178">
-        <f t="shared" si="2"/>
-        <v>33.54941790000003</v>
+        <v>149.10724180000003</v>
       </c>
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="B179">
         <v>12.904999999999999</v>
@@ -5138,13 +4971,12 @@
         <v>2491822.9640000011</v>
       </c>
       <c r="E179">
-        <f t="shared" si="2"/>
-        <v>24.918229640000011</v>
+        <v>114.08940097999998</v>
       </c>
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="B180">
         <v>10.782999999999999</v>
@@ -5156,13 +4988,12 @@
         <v>3238531.9400000013</v>
       </c>
       <c r="E180">
-        <f t="shared" si="2"/>
-        <v>32.385319400000014</v>
+        <v>112.05923695999999</v>
       </c>
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="B181">
         <v>12.848000000000001</v>
@@ -5174,13 +5005,12 @@
         <v>1825460.5100000007</v>
       </c>
       <c r="E181">
-        <f t="shared" si="2"/>
-        <v>18.254605100000006</v>
+        <v>64.984655480000001</v>
       </c>
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B182">
         <v>13.081</v>
@@ -5192,13 +5022,12 @@
         <v>2461829.9600000009</v>
       </c>
       <c r="E182">
-        <f t="shared" si="2"/>
-        <v>24.618299600000007</v>
+        <v>72.725796139999986</v>
       </c>
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B183">
         <v>13.087999999999999</v>
@@ -5210,13 +5039,12 @@
         <v>2447627.0720000011</v>
       </c>
       <c r="E183">
-        <f t="shared" si="2"/>
-        <v>24.476270720000009</v>
+        <v>103.13068804</v>
       </c>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="B184">
         <v>12.901</v>
@@ -5228,13 +5056,12 @@
         <v>2272471.6600000015</v>
       </c>
       <c r="E184">
-        <f t="shared" si="2"/>
-        <v>22.724716600000015</v>
+        <v>88.392441529999985</v>
       </c>
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="B185">
         <v>13.122999999999999</v>
@@ -5246,13 +5073,12 @@
         <v>2377245.9365000012</v>
       </c>
       <c r="E185">
-        <f t="shared" si="2"/>
-        <v>23.772459365000014</v>
+        <v>111.28124525999999</v>
       </c>
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="B186">
         <v>13.061</v>
@@ -5264,13 +5090,12 @@
         <v>1904623.0600000017</v>
       </c>
       <c r="E186">
-        <f t="shared" si="2"/>
-        <v>19.046230600000015</v>
+        <v>77.231467109999997</v>
       </c>
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="B187">
         <v>15.374000000000001</v>
@@ -5282,13 +5107,12 @@
         <v>2069780.154000001</v>
       </c>
       <c r="E187">
-        <f t="shared" si="2"/>
-        <v>20.697801540000011</v>
+        <v>87.698540390000005</v>
       </c>
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="B188">
         <v>12.98</v>
@@ -5300,13 +5124,12 @@
         <v>2818717.2600000012</v>
       </c>
       <c r="E188">
-        <f t="shared" si="2"/>
-        <v>28.187172600000011</v>
+        <v>104.07446787000002</v>
       </c>
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="B189">
         <v>15.590999999999999</v>
@@ -5318,13 +5141,12 @@
         <v>3060276.8200000017</v>
       </c>
       <c r="E189">
-        <f t="shared" si="2"/>
-        <v>30.602768200000018</v>
+        <v>135.95829358999998</v>
       </c>
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="B190">
         <v>10.145</v>
@@ -5336,13 +5158,12 @@
         <v>1064298.9200000002</v>
       </c>
       <c r="E190">
-        <f t="shared" si="2"/>
-        <v>10.642989200000002</v>
+        <v>14.045238480000002</v>
       </c>
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="B191">
         <v>15.863</v>
@@ -5354,13 +5175,12 @@
         <v>1619700.4400000002</v>
       </c>
       <c r="E191">
-        <f t="shared" si="2"/>
-        <v>16.197004400000001</v>
+        <v>84.033680230000002</v>
       </c>
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="B192">
         <v>9.6590000000000007</v>
@@ -5372,13 +5192,12 @@
         <v>1152704.8699999996</v>
       </c>
       <c r="E192">
-        <f t="shared" si="2"/>
-        <v>11.527048699999996</v>
+        <v>37.354825779999999</v>
       </c>
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="B193">
         <v>10.494999999999999</v>
@@ -5390,13 +5209,12 @@
         <v>1246903.5000000005</v>
       </c>
       <c r="E193">
-        <f t="shared" si="2"/>
-        <v>12.469035000000005</v>
+        <v>29.023138829999994</v>
       </c>
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="B194">
         <v>15.417</v>
@@ -5408,13 +5226,12 @@
         <v>1547088.3500000008</v>
       </c>
       <c r="E194">
-        <f t="shared" si="2"/>
-        <v>15.470883500000008</v>
+        <v>69.757230109999995</v>
       </c>
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="B195">
         <v>12.904999999999999</v>
@@ -5426,13 +5243,12 @@
         <v>2286100.7300000014</v>
       </c>
       <c r="E195">
-        <f t="shared" ref="E195:E258" si="3">D195/100000</f>
-        <v>22.861007300000015</v>
+        <v>106.29918688999999</v>
       </c>
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="B196">
         <v>13.125</v>
@@ -5444,13 +5260,12 @@
         <v>1151716.8999999999</v>
       </c>
       <c r="E196">
-        <f t="shared" si="3"/>
-        <v>11.517168999999999</v>
+        <v>68.103641469999985</v>
       </c>
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="B197">
         <v>15.587999999999999</v>
@@ -5462,13 +5277,12 @@
         <v>1104889.1099999999</v>
       </c>
       <c r="E197">
-        <f t="shared" si="3"/>
-        <v>11.048891099999999</v>
+        <v>51.234574999999992</v>
       </c>
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="B198">
         <v>14.612</v>
@@ -5480,13 +5294,12 @@
         <v>1179200.3599999999</v>
       </c>
       <c r="E198">
-        <f t="shared" si="3"/>
-        <v>11.792003599999999</v>
+        <v>62.395336719999996</v>
       </c>
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="B199">
         <v>12.942</v>
@@ -5498,13 +5311,12 @@
         <v>2232226.8000000012</v>
       </c>
       <c r="E199">
-        <f t="shared" si="3"/>
-        <v>22.322268000000012</v>
+        <v>81.512843259999997</v>
       </c>
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="B200">
         <v>13.029</v>
@@ -5516,13 +5328,12 @@
         <v>1993428.0500000007</v>
       </c>
       <c r="E200">
-        <f t="shared" si="3"/>
-        <v>19.934280500000007</v>
+        <v>83.686852039999991</v>
       </c>
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B201">
         <v>12.893000000000001</v>
@@ -5534,13 +5345,12 @@
         <v>1750879.5440000002</v>
       </c>
       <c r="E201">
-        <f t="shared" si="3"/>
-        <v>17.508795440000004</v>
+        <v>68.185226159999999</v>
       </c>
     </row>
     <row r="202" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="B202">
         <v>13.095000000000001</v>
@@ -5552,13 +5362,12 @@
         <v>2131368.8025000012</v>
       </c>
       <c r="E202">
-        <f t="shared" si="3"/>
-        <v>21.313688025000012</v>
+        <v>80.240993020000005</v>
       </c>
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="B203">
         <v>16.167999999999999</v>
@@ -5570,13 +5379,12 @@
         <v>1074607.1400000001</v>
       </c>
       <c r="E203">
-        <f t="shared" si="3"/>
-        <v>10.746071400000002</v>
+        <v>42.557481380000013</v>
       </c>
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="B204">
         <v>12.824</v>
@@ -5588,13 +5396,12 @@
         <v>1103620.3900000001</v>
       </c>
       <c r="E204">
-        <f t="shared" si="3"/>
-        <v>11.036203900000002</v>
+        <v>66.308375470000001</v>
       </c>
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B205">
         <v>15.555</v>
@@ -5606,13 +5413,12 @@
         <v>1684405.1300000008</v>
       </c>
       <c r="E205">
-        <f t="shared" si="3"/>
-        <v>16.844051300000007</v>
+        <v>72.107317699999996</v>
       </c>
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="B206">
         <v>15.164</v>
@@ -5624,13 +5430,12 @@
         <v>1686362.0300000003</v>
       </c>
       <c r="E206">
-        <f t="shared" si="3"/>
-        <v>16.863620300000001</v>
+        <v>61.940201080000008</v>
       </c>
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="B207">
         <v>15.391</v>
@@ -5642,13 +5447,12 @@
         <v>2001833.9050000005</v>
       </c>
       <c r="E207">
-        <f t="shared" si="3"/>
-        <v>20.018339050000005</v>
+        <v>116.30465114</v>
       </c>
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="B208">
         <v>10.756</v>
@@ -5660,13 +5464,12 @@
         <v>1276740.6905</v>
       </c>
       <c r="E208">
-        <f t="shared" si="3"/>
-        <v>12.767406905</v>
+        <v>66.855763359999997</v>
       </c>
     </row>
     <row r="209" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="B209">
         <v>13.11</v>
@@ -5678,13 +5481,12 @@
         <v>1597562.4300000004</v>
       </c>
       <c r="E209">
-        <f t="shared" si="3"/>
-        <v>15.975624300000003</v>
+        <v>88.478678209999998</v>
       </c>
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="B210">
         <v>13.164</v>
@@ -5696,13 +5498,12 @@
         <v>1771764.0499999996</v>
       </c>
       <c r="E210">
-        <f t="shared" si="3"/>
-        <v>17.717640499999995</v>
+        <v>75.598257910000001</v>
       </c>
     </row>
     <row r="211" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="B211">
         <v>12.997</v>
@@ -5714,13 +5515,12 @@
         <v>1918009.4200000009</v>
       </c>
       <c r="E211">
-        <f t="shared" si="3"/>
-        <v>19.18009420000001</v>
+        <v>112.48154805000001</v>
       </c>
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B212">
         <v>15.333</v>
@@ -5732,13 +5532,12 @@
         <v>3416040.9000000027</v>
       </c>
       <c r="E212">
-        <f t="shared" si="3"/>
-        <v>34.16040900000003</v>
+        <v>105.4919814</v>
       </c>
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="B213">
         <v>24.890999999999998</v>
@@ -5750,13 +5549,12 @@
         <v>1074884.3700000001</v>
       </c>
       <c r="E213">
-        <f t="shared" si="3"/>
-        <v>10.748843700000002</v>
+        <v>42.460759999999993</v>
       </c>
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="B214">
         <v>25.337</v>
@@ -5768,13 +5566,12 @@
         <v>1080862.4299999997</v>
       </c>
       <c r="E214">
-        <f t="shared" si="3"/>
-        <v>10.808624299999996</v>
+        <v>46.730499999999999</v>
       </c>
     </row>
     <row r="215" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="B215">
         <v>26.253</v>
@@ -5786,13 +5583,12 @@
         <v>2241618.9529000013</v>
       </c>
       <c r="E215">
-        <f t="shared" si="3"/>
-        <v>22.416189529000015</v>
+        <v>131.71890000000002</v>
       </c>
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="B216">
         <v>26.841000000000001</v>
@@ -5804,13 +5600,12 @@
         <v>2102665.3810000005</v>
       </c>
       <c r="E216">
-        <f t="shared" si="3"/>
-        <v>21.026653810000006</v>
+        <v>114.2557</v>
       </c>
     </row>
     <row r="217" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="B217">
         <v>26.3</v>
@@ -5822,13 +5617,12 @@
         <v>2045125.4200000013</v>
       </c>
       <c r="E217">
-        <f t="shared" si="3"/>
-        <v>20.451254200000012</v>
+        <v>84.189700000000016</v>
       </c>
     </row>
     <row r="218" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="B218">
         <v>25.771000000000001</v>
@@ -5840,13 +5634,12 @@
         <v>1916168.3100000003</v>
       </c>
       <c r="E218">
-        <f t="shared" si="3"/>
-        <v>19.161683100000001</v>
+        <v>91.457700000000003</v>
       </c>
     </row>
     <row r="219" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B219">
         <v>24.632999999999999</v>
@@ -5858,13 +5651,12 @@
         <v>1575479.8935000005</v>
       </c>
       <c r="E219">
-        <f t="shared" si="3"/>
-        <v>15.754798935000005</v>
+        <v>70.680704999999989</v>
       </c>
     </row>
     <row r="220" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B220">
         <v>26.227</v>
@@ -5876,13 +5668,12 @@
         <v>2536374.8325000005</v>
       </c>
       <c r="E220">
-        <f t="shared" si="3"/>
-        <v>25.363748325000003</v>
+        <v>126.09799999999998</v>
       </c>
     </row>
     <row r="221" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="B221">
         <v>25.151</v>
@@ -5894,13 +5685,12 @@
         <v>1751246.8630000001</v>
       </c>
       <c r="E221">
-        <f t="shared" si="3"/>
-        <v>17.512468630000001</v>
+        <v>82.724900000000019</v>
       </c>
     </row>
     <row r="222" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="B222">
         <v>25.42</v>
@@ -5912,13 +5702,12 @@
         <v>1797473.0665000007</v>
       </c>
       <c r="E222">
-        <f t="shared" si="3"/>
-        <v>17.974730665000006</v>
+        <v>86.911927500000019</v>
       </c>
     </row>
     <row r="223" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="B223">
         <v>25.456</v>
@@ -5930,13 +5719,12 @@
         <v>2167124.5200000005</v>
       </c>
       <c r="E223">
-        <f t="shared" si="3"/>
-        <v>21.671245200000005</v>
+        <v>111.28475750000004</v>
       </c>
     </row>
     <row r="224" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="B224">
         <v>25.123000000000001</v>
@@ -5948,13 +5736,12 @@
         <v>1143110.5349999997</v>
       </c>
       <c r="E224">
-        <f t="shared" si="3"/>
-        <v>11.431105349999998</v>
+        <v>56.317099999999989</v>
       </c>
     </row>
     <row r="225" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="B225">
         <v>26.251000000000001</v>
@@ -5966,13 +5753,12 @@
         <v>2602516.9700000002</v>
       </c>
       <c r="E225">
-        <f t="shared" si="3"/>
-        <v>26.025169700000003</v>
+        <v>83.717000000000013</v>
       </c>
     </row>
     <row r="226" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="B226">
         <v>26.58</v>
@@ -5984,13 +5770,12 @@
         <v>1851393.8725000001</v>
       </c>
       <c r="E226">
-        <f t="shared" si="3"/>
-        <v>18.513938724999999</v>
+        <v>86.118099999999998</v>
       </c>
     </row>
     <row r="227" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="B227">
         <v>28.010999999999999</v>
@@ -6002,13 +5787,12 @@
         <v>1230325.7124999997</v>
       </c>
       <c r="E227">
-        <f t="shared" si="3"/>
-        <v>12.303257124999996</v>
+        <v>65.835999999999999</v>
       </c>
     </row>
     <row r="228" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="B228">
         <v>26.42</v>
@@ -6020,13 +5804,12 @@
         <v>1965669.82</v>
       </c>
       <c r="E228">
-        <f t="shared" si="3"/>
-        <v>19.656698200000001</v>
+        <v>93.571700000000007</v>
       </c>
     </row>
     <row r="229" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="B229">
         <v>26.231000000000002</v>
@@ -6038,13 +5821,12 @@
         <v>1581321.5078000003</v>
       </c>
       <c r="E229">
-        <f t="shared" si="3"/>
-        <v>15.813215078000002</v>
+        <v>84.747500000000002</v>
       </c>
     </row>
     <row r="230" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="B230">
         <v>26.826000000000001</v>
@@ -6056,13 +5838,12 @@
         <v>1898258.2930000003</v>
       </c>
       <c r="E230">
-        <f t="shared" si="3"/>
-        <v>18.982582930000003</v>
+        <v>107.69229999999999</v>
       </c>
     </row>
     <row r="231" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="B231">
         <v>26.21</v>
@@ -6074,13 +5855,12 @@
         <v>2705208.1045000022</v>
       </c>
       <c r="E231">
-        <f t="shared" si="3"/>
-        <v>27.052081045000023</v>
+        <v>139.30289999999999</v>
       </c>
     </row>
     <row r="232" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="B232">
         <v>25.138000000000002</v>
@@ -6092,13 +5872,12 @@
         <v>3550826.2640000037</v>
       </c>
       <c r="E232">
-        <f t="shared" si="3"/>
-        <v>35.508262640000034</v>
+        <v>157.08910000000003</v>
       </c>
     </row>
     <row r="233" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="B233">
         <v>26.465</v>
@@ -6110,13 +5889,12 @@
         <v>2798573.0400000005</v>
       </c>
       <c r="E233">
-        <f t="shared" si="3"/>
-        <v>27.985730400000005</v>
+        <v>136.75980000000001</v>
       </c>
     </row>
     <row r="234" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="B234">
         <v>25.45</v>
@@ -6128,13 +5906,12 @@
         <v>3675896.1959999986</v>
       </c>
       <c r="E234">
-        <f t="shared" si="3"/>
-        <v>36.758961959999986</v>
+        <v>165.70640750000001</v>
       </c>
     </row>
     <row r="235" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="B235">
         <v>25.343</v>
@@ -6146,13 +5923,12 @@
         <v>1950675.8100000008</v>
       </c>
       <c r="E235">
-        <f t="shared" si="3"/>
-        <v>19.506758100000006</v>
+        <v>75.549600000000012</v>
       </c>
     </row>
     <row r="236" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="B236">
         <v>25.167999999999999</v>
@@ -6164,13 +5940,12 @@
         <v>1740886.92</v>
       </c>
       <c r="E236">
-        <f t="shared" si="3"/>
-        <v>17.408869199999998</v>
+        <v>78.353000000000009</v>
       </c>
     </row>
     <row r="237" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="B237">
         <v>26.210999999999999</v>
@@ -6182,13 +5957,12 @@
         <v>3883837.056400002</v>
       </c>
       <c r="E237">
-        <f t="shared" si="3"/>
-        <v>38.838370564000023</v>
+        <v>200.32319999999999</v>
       </c>
     </row>
     <row r="238" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="B238">
         <v>24.876999999999999</v>
@@ -6200,13 +5974,12 @@
         <v>3223989.21</v>
       </c>
       <c r="E238">
-        <f t="shared" si="3"/>
-        <v>32.239892099999999</v>
+        <v>68.567399999999992</v>
       </c>
     </row>
     <row r="239" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="B239">
         <v>28.010999999999999</v>
@@ -6218,13 +5991,12 @@
         <v>2632731.0150000015</v>
       </c>
       <c r="E239">
-        <f t="shared" si="3"/>
-        <v>26.327310150000017</v>
+        <v>111.0064</v>
       </c>
     </row>
     <row r="240" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="B240">
         <v>25.454999999999998</v>
@@ -6236,13 +6008,12 @@
         <v>2454580.7627000008</v>
       </c>
       <c r="E240">
-        <f t="shared" si="3"/>
-        <v>24.545807627000009</v>
+        <v>126.10767999999999</v>
       </c>
     </row>
     <row r="241" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="B241">
         <v>26.277000000000001</v>
@@ -6254,13 +6025,12 @@
         <v>2563707.9975000005</v>
       </c>
       <c r="E241">
-        <f t="shared" si="3"/>
-        <v>25.637079975000006</v>
+        <v>115.5759</v>
       </c>
     </row>
     <row r="242" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="B242">
         <v>26.803000000000001</v>
@@ -6272,13 +6042,12 @@
         <v>4645503.3800000036</v>
       </c>
       <c r="E242">
-        <f t="shared" si="3"/>
-        <v>46.455033800000038</v>
+        <v>215.00959999999998</v>
       </c>
     </row>
     <row r="243" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="B243">
         <v>26.216000000000001</v>
@@ -6290,13 +6059,12 @@
         <v>1774811.3699999999</v>
       </c>
       <c r="E243">
-        <f t="shared" si="3"/>
-        <v>17.748113699999998</v>
+        <v>83.307749999999999</v>
       </c>
     </row>
     <row r="244" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="B244">
         <v>27.622</v>
@@ -6308,13 +6076,12 @@
         <v>2030054.4740000011</v>
       </c>
       <c r="E244">
-        <f t="shared" si="3"/>
-        <v>20.30054474000001</v>
+        <v>101.46800000000002</v>
       </c>
     </row>
     <row r="245" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="B245">
         <v>25.202000000000002</v>
@@ -6326,13 +6093,12 @@
         <v>2040609.0250000006</v>
       </c>
       <c r="E245">
-        <f t="shared" si="3"/>
-        <v>20.406090250000005</v>
+        <v>102.41480000000001</v>
       </c>
     </row>
     <row r="246" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="B246">
         <v>26.513999999999999</v>
@@ -6344,13 +6110,12 @@
         <v>1157036.2479999997</v>
       </c>
       <c r="E246">
-        <f t="shared" si="3"/>
-        <v>11.570362479999996</v>
+        <v>85.721899999999991</v>
       </c>
     </row>
     <row r="247" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="B247">
         <v>25.221</v>
@@ -6362,13 +6127,12 @@
         <v>2177290.5450000004</v>
       </c>
       <c r="E247">
-        <f t="shared" si="3"/>
-        <v>21.772905450000003</v>
+        <v>75.193900000000014</v>
       </c>
     </row>
     <row r="248" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="B248">
         <v>26.469000000000001</v>
@@ -6380,13 +6144,12 @@
         <v>1192178.595</v>
       </c>
       <c r="E248">
-        <f t="shared" si="3"/>
-        <v>11.92178595</v>
+        <v>60.352799999999988</v>
       </c>
     </row>
     <row r="249" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="B249">
         <v>26.196000000000002</v>
@@ -6398,13 +6161,12 @@
         <v>1638049.9300000004</v>
       </c>
       <c r="E249">
-        <f t="shared" si="3"/>
-        <v>16.380499300000004</v>
+        <v>77.684399999999982</v>
       </c>
     </row>
     <row r="250" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="B250">
         <v>26.477</v>
@@ -6416,13 +6178,12 @@
         <v>1198368.3500000003</v>
       </c>
       <c r="E250">
-        <f t="shared" si="3"/>
-        <v>11.983683500000003</v>
+        <v>56.085100000000004</v>
       </c>
     </row>
     <row r="251" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="B251">
         <v>27.626999999999999</v>
@@ -6434,13 +6195,12 @@
         <v>1375806.11</v>
       </c>
       <c r="E251">
-        <f t="shared" si="3"/>
-        <v>13.758061100000001</v>
+        <v>53.748599999999989</v>
       </c>
     </row>
     <row r="252" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="B252">
         <v>26.753</v>
@@ -6452,13 +6212,12 @@
         <v>510076.44</v>
       </c>
       <c r="E252">
-        <f t="shared" si="3"/>
-        <v>5.1007644000000001</v>
+        <v>22.082508000000001</v>
       </c>
     </row>
     <row r="253" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="B253">
         <v>27.181999999999999</v>
@@ -6470,13 +6229,12 @@
         <v>568725.01</v>
       </c>
       <c r="E253">
-        <f t="shared" si="3"/>
-        <v>5.6872501</v>
+        <v>26.165399999999998</v>
       </c>
     </row>
     <row r="254" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="B254">
         <v>23.853000000000002</v>
@@ -6488,13 +6246,12 @@
         <v>543588.8899999999</v>
       </c>
       <c r="E254">
-        <f t="shared" si="3"/>
-        <v>5.4358888999999992</v>
+        <v>41.905200000000001</v>
       </c>
     </row>
     <row r="255" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="B255">
         <v>23.753</v>
@@ -6506,13 +6263,12 @@
         <v>1069336.4900000002</v>
       </c>
       <c r="E255">
-        <f t="shared" si="3"/>
-        <v>10.693364900000002</v>
+        <v>898.03800000000024</v>
       </c>
     </row>
     <row r="256" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="B256">
         <v>23.734000000000002</v>
@@ -6524,13 +6280,12 @@
         <v>1559050.7699999996</v>
       </c>
       <c r="E256">
-        <f t="shared" si="3"/>
-        <v>15.590507699999996</v>
+        <v>13.4594</v>
       </c>
     </row>
     <row r="257" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="B257">
         <v>27.314</v>
@@ -6542,13 +6297,12 @@
         <v>1896307.7750000006</v>
       </c>
       <c r="E257">
-        <f t="shared" si="3"/>
-        <v>18.963077750000007</v>
+        <v>109.86959999999999</v>
       </c>
     </row>
     <row r="258" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="B258">
         <v>26.527000000000001</v>
@@ -6560,13 +6314,12 @@
         <v>1962784.350000001</v>
       </c>
       <c r="E258">
-        <f t="shared" si="3"/>
-        <v>19.627843500000012</v>
+        <v>128.60566</v>
       </c>
     </row>
     <row r="259" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="B259">
         <v>24.824999999999999</v>
@@ -6578,13 +6331,12 @@
         <v>2434991.2800000007</v>
       </c>
       <c r="E259">
-        <f t="shared" ref="E259:E322" si="4">D259/100000</f>
-        <v>24.349912800000006</v>
+        <v>571.54199999999992</v>
       </c>
     </row>
     <row r="260" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B260">
         <v>27.484999999999999</v>
@@ -6596,13 +6348,12 @@
         <v>1806396.1950000008</v>
       </c>
       <c r="E260">
-        <f t="shared" si="4"/>
-        <v>18.063961950000007</v>
+        <v>122.977441</v>
       </c>
     </row>
     <row r="261" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="B261">
         <v>26.709</v>
@@ -6614,13 +6365,12 @@
         <v>2593651.9600000014</v>
       </c>
       <c r="E261">
-        <f t="shared" si="4"/>
-        <v>25.936519600000015</v>
+        <v>131.06546749999998</v>
       </c>
     </row>
     <row r="262" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="B262">
         <v>26.986999999999998</v>
@@ -6632,13 +6382,12 @@
         <v>1848911.9900000007</v>
       </c>
       <c r="E262">
-        <f t="shared" si="4"/>
-        <v>18.489119900000006</v>
+        <v>95.626099999999994</v>
       </c>
     </row>
     <row r="263" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="B263">
         <v>26.690999999999999</v>
@@ -6650,13 +6399,12 @@
         <v>1714893.6225000008</v>
       </c>
       <c r="E263">
-        <f t="shared" si="4"/>
-        <v>17.148936225000007</v>
+        <v>106.74790000000002</v>
       </c>
     </row>
     <row r="264" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="B264">
         <v>26.728999999999999</v>
@@ -6668,13 +6416,12 @@
         <v>2284491.2720000013</v>
       </c>
       <c r="E264">
-        <f t="shared" si="4"/>
-        <v>22.844912720000014</v>
+        <v>123.20492549999997</v>
       </c>
     </row>
     <row r="265" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="B265">
         <v>24.795000000000002</v>
@@ -6686,13 +6433,12 @@
         <v>1242039.3400000003</v>
       </c>
       <c r="E265">
-        <f t="shared" si="4"/>
-        <v>12.420393400000004</v>
+        <v>284.04599999999999</v>
       </c>
     </row>
     <row r="266" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="B266">
         <v>23.786999999999999</v>
@@ -6704,13 +6450,12 @@
         <v>1194645.2550000001</v>
       </c>
       <c r="E266">
-        <f t="shared" si="4"/>
-        <v>11.946452550000002</v>
+        <v>995.34720000000016</v>
       </c>
     </row>
     <row r="267" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="B267">
         <v>27.294</v>
@@ -6722,13 +6467,12 @@
         <v>1588148.5199999998</v>
       </c>
       <c r="E267">
-        <f t="shared" si="4"/>
-        <v>15.881485199999998</v>
+        <v>56.994799999999998</v>
       </c>
     </row>
     <row r="268" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="B268">
         <v>27.492000000000001</v>
@@ -6740,13 +6484,12 @@
         <v>2930447.7900000014</v>
       </c>
       <c r="E268">
-        <f t="shared" si="4"/>
-        <v>29.304477900000013</v>
+        <v>162.22768799999997</v>
       </c>
     </row>
     <row r="269" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="B269">
         <v>27.359000000000002</v>
@@ -6758,13 +6501,12 @@
         <v>1871897.3200000003</v>
       </c>
       <c r="E269">
-        <f t="shared" si="4"/>
-        <v>18.718973200000004</v>
+        <v>93.859049500000012</v>
       </c>
     </row>
     <row r="270" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="B270">
         <v>27.062999999999999</v>
@@ -6776,13 +6518,12 @@
         <v>1478735.0900000003</v>
       </c>
       <c r="E270">
-        <f t="shared" si="4"/>
-        <v>14.787350900000003</v>
+        <v>72.166000000000011</v>
       </c>
     </row>
     <row r="271" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="B271">
         <v>27.344999999999999</v>
@@ -6794,13 +6535,12 @@
         <v>1503425.0000000005</v>
       </c>
       <c r="E271">
-        <f t="shared" si="4"/>
-        <v>15.034250000000005</v>
+        <v>77.258599999999987</v>
       </c>
     </row>
     <row r="272" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="B272">
         <v>27.042999999999999</v>
@@ -6812,13 +6552,12 @@
         <v>1511007.57</v>
       </c>
       <c r="E272">
-        <f t="shared" si="4"/>
-        <v>15.110075700000001</v>
+        <v>72.496999999999986</v>
       </c>
     </row>
     <row r="273" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="B273">
         <v>26.747</v>
@@ -6830,13 +6569,12 @@
         <v>3615376.678000004</v>
       </c>
       <c r="E273">
-        <f t="shared" si="4"/>
-        <v>36.153766780000041</v>
+        <v>186.42242150000004</v>
       </c>
     </row>
     <row r="274" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="B274">
         <v>27.329000000000001</v>
@@ -6848,13 +6586,12 @@
         <v>3072811.5200000019</v>
       </c>
       <c r="E274">
-        <f t="shared" si="4"/>
-        <v>30.728115200000019</v>
+        <v>150.11020000000002</v>
       </c>
     </row>
     <row r="275" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="B275">
         <v>27.04</v>
@@ -6866,13 +6603,12 @@
         <v>1741330.9500000009</v>
       </c>
       <c r="E275">
-        <f t="shared" si="4"/>
-        <v>17.413309500000008</v>
+        <v>71.230499999999992</v>
       </c>
     </row>
     <row r="276" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="B276">
         <v>26.725000000000001</v>
@@ -6884,13 +6620,12 @@
         <v>4084671.510000004</v>
       </c>
       <c r="E276">
-        <f t="shared" si="4"/>
-        <v>40.84671510000004</v>
+        <v>222.12216100000001</v>
       </c>
     </row>
     <row r="277" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="B277">
         <v>26.702999999999999</v>
@@ -6902,13 +6637,12 @@
         <v>3240192.8535000016</v>
       </c>
       <c r="E277">
-        <f t="shared" si="4"/>
-        <v>32.401928535000017</v>
+        <v>243.76793999999998</v>
       </c>
     </row>
     <row r="278" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="B278">
         <v>27.175000000000001</v>
@@ -6920,13 +6654,12 @@
         <v>1377782.6900000004</v>
       </c>
       <c r="E278">
-        <f t="shared" si="4"/>
-        <v>13.777826900000004</v>
+        <v>59.308600000000006</v>
       </c>
     </row>
     <row r="279" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="B279">
         <v>26.719000000000001</v>
@@ -6938,13 +6671,12 @@
         <v>3446706.3360000025</v>
       </c>
       <c r="E279">
-        <f t="shared" si="4"/>
-        <v>34.467063360000026</v>
+        <v>200.4813</v>
       </c>
     </row>
     <row r="280" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="B280">
         <v>27.48</v>
@@ -6956,13 +6688,12 @@
         <v>2327134.4275000012</v>
       </c>
       <c r="E280">
-        <f t="shared" si="4"/>
-        <v>23.271344275000011</v>
+        <v>152.12701850000002</v>
       </c>
     </row>
     <row r="281" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="B281">
         <v>26.855</v>
@@ -6974,13 +6705,12 @@
         <v>1920996.9850000003</v>
       </c>
       <c r="E281">
-        <f t="shared" si="4"/>
-        <v>19.209969850000004</v>
+        <v>100.023278</v>
       </c>
     </row>
     <row r="282" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="B282">
         <v>26.753</v>
@@ -6992,13 +6722,12 @@
         <v>1744236.5700000017</v>
       </c>
       <c r="E282">
-        <f t="shared" si="4"/>
-        <v>17.442365700000018</v>
+        <v>65.619122499999989</v>
       </c>
     </row>
     <row r="283" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="B283">
         <v>23.829000000000001</v>
@@ -7010,13 +6739,12 @@
         <v>1921844.3500000006</v>
       </c>
       <c r="E283">
-        <f t="shared" si="4"/>
-        <v>19.218443500000006</v>
+        <v>59.614799999999988</v>
       </c>
     </row>
     <row r="284" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="B284">
         <v>23.856000000000002</v>
@@ -7028,13 +6756,12 @@
         <v>1808025.7400000002</v>
       </c>
       <c r="E284">
-        <f t="shared" si="4"/>
-        <v>18.080257400000001</v>
+        <v>92.101200000000006</v>
       </c>
     </row>
     <row r="285" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="B285">
         <v>26.765999999999998</v>
@@ -7046,13 +6773,12 @@
         <v>2074607.0350000008</v>
       </c>
       <c r="E285">
-        <f t="shared" si="4"/>
-        <v>20.746070350000007</v>
+        <v>87.221199999999996</v>
       </c>
     </row>
     <row r="286" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="B286">
         <v>27.33</v>
@@ -7064,13 +6790,12 @@
         <v>1502978.3900000013</v>
       </c>
       <c r="E286">
-        <f t="shared" si="4"/>
-        <v>15.029783900000012</v>
+        <v>44.382999999999996</v>
       </c>
     </row>
     <row r="287" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="B287">
         <v>27.164999999999999</v>
@@ -7082,13 +6807,12 @@
         <v>1291323.6700000002</v>
       </c>
       <c r="E287">
-        <f t="shared" si="4"/>
-        <v>12.913236700000002</v>
+        <v>72.455500000000001</v>
       </c>
     </row>
     <row r="288" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="B288">
         <v>24.329000000000001</v>
@@ -7100,13 +6824,12 @@
         <v>2355886.9200000004</v>
       </c>
       <c r="E288">
-        <f t="shared" si="4"/>
-        <v>23.558869200000004</v>
+        <v>228.60599999999999</v>
       </c>
     </row>
     <row r="289" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="B289">
         <v>27.238</v>
@@ -7118,13 +6841,12 @@
         <v>3031148.0500000031</v>
       </c>
       <c r="E289">
-        <f t="shared" si="4"/>
-        <v>30.31148050000003</v>
+        <v>106.68099200000002</v>
       </c>
     </row>
     <row r="290" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="B290">
         <v>17.632999999999999</v>
@@ -7136,13 +6858,12 @@
         <v>2400814.0980000012</v>
       </c>
       <c r="E290">
-        <f t="shared" si="4"/>
-        <v>24.008140980000011</v>
+        <v>118.29097999999999</v>
       </c>
     </row>
     <row r="291" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="B291">
         <v>16.544</v>
@@ -7154,13 +6875,12 @@
         <v>1827437.2000000004</v>
       </c>
       <c r="E291">
-        <f t="shared" si="4"/>
-        <v>18.274372000000003</v>
+        <v>56.558839999999982</v>
       </c>
     </row>
     <row r="292" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="B292">
         <v>14.676</v>
@@ -7172,13 +6892,12 @@
         <v>2439325.1669999999</v>
       </c>
       <c r="E292">
-        <f t="shared" si="4"/>
-        <v>24.393251669999998</v>
+        <v>99.75030000000001</v>
       </c>
     </row>
     <row r="293" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="B293">
         <v>15.276</v>
@@ -7190,13 +6909,12 @@
         <v>2126889.5025000009</v>
       </c>
       <c r="E293">
-        <f t="shared" si="4"/>
-        <v>21.26889502500001</v>
+        <v>76.357099999999988</v>
       </c>
     </row>
     <row r="294" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="B294">
         <v>16.709</v>
@@ -7208,13 +6926,12 @@
         <v>1886286.7700000009</v>
       </c>
       <c r="E294">
-        <f t="shared" si="4"/>
-        <v>18.86286770000001</v>
+        <v>65.989639999999994</v>
       </c>
     </row>
     <row r="295" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="B295">
         <v>15.512</v>
@@ -7226,13 +6943,12 @@
         <v>2055151.5925000007</v>
       </c>
       <c r="E295">
-        <f t="shared" si="4"/>
-        <v>20.551515925000007</v>
+        <v>70.176840000000013</v>
       </c>
     </row>
     <row r="296" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="B296">
         <v>16.68</v>
@@ -7244,13 +6960,12 @@
         <v>1874581.7225000001</v>
       </c>
       <c r="E296">
-        <f t="shared" si="4"/>
-        <v>18.745817225000003</v>
+        <v>80.123260000000016</v>
       </c>
     </row>
     <row r="297" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="B297">
         <v>16.481999999999999</v>
@@ -7262,13 +6977,12 @@
         <v>1657880.0600000003</v>
       </c>
       <c r="E297">
-        <f t="shared" si="4"/>
-        <v>16.578800600000005</v>
+        <v>73.270079999999993</v>
       </c>
     </row>
     <row r="298" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="B298">
         <v>16.809000000000001</v>
@@ -7280,13 +6994,12 @@
         <v>2079508.2600000002</v>
       </c>
       <c r="E298">
-        <f t="shared" si="4"/>
-        <v>20.795082600000004</v>
+        <v>113.30992000000002</v>
       </c>
     </row>
     <row r="299" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="B299">
         <v>17.692</v>
@@ -7298,13 +7011,12 @@
         <v>936408.26799999992</v>
       </c>
       <c r="E299">
-        <f t="shared" si="4"/>
-        <v>9.3640826799999992</v>
+        <v>43.526119999999999</v>
       </c>
     </row>
     <row r="300" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="B300">
         <v>16.844000000000001</v>
@@ -7316,13 +7028,12 @@
         <v>2022899.0860000006</v>
       </c>
       <c r="E300">
-        <f t="shared" si="4"/>
-        <v>20.228990860000007</v>
+        <v>108.32341999999998</v>
       </c>
     </row>
     <row r="301" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="B301">
         <v>17.010000000000002</v>
@@ -7334,13 +7045,12 @@
         <v>1712647.3840000001</v>
       </c>
       <c r="E301">
-        <f t="shared" si="4"/>
-        <v>17.126473839999999</v>
+        <v>51.793279999999996</v>
       </c>
     </row>
     <row r="302" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="B302">
         <v>16.957999999999998</v>
@@ -7352,13 +7062,12 @@
         <v>1668319.6300000001</v>
       </c>
       <c r="E302">
-        <f t="shared" si="4"/>
-        <v>16.683196300000002</v>
+        <v>68.978099999999998</v>
       </c>
     </row>
     <row r="303" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="B303">
         <v>17.78</v>
@@ -7370,13 +7079,12 @@
         <v>1717350.6459999999</v>
       </c>
       <c r="E303">
-        <f t="shared" si="4"/>
-        <v>17.173506459999999</v>
+        <v>69.737560000000002</v>
       </c>
     </row>
     <row r="304" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="B304">
         <v>17.710999999999999</v>
@@ -7388,13 +7096,12 @@
         <v>2540981.3370000022</v>
       </c>
       <c r="E304">
-        <f t="shared" si="4"/>
-        <v>25.409813370000023</v>
+        <v>116.13984000000004</v>
       </c>
     </row>
     <row r="305" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="B305">
         <v>17.738</v>
@@ -7406,13 +7113,12 @@
         <v>2228483.6345000011</v>
       </c>
       <c r="E305">
-        <f t="shared" si="4"/>
-        <v>22.284836345000009</v>
+        <v>100.22103999999999</v>
       </c>
     </row>
     <row r="306" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="B306">
         <v>17.687000000000001</v>
@@ -7424,13 +7130,12 @@
         <v>2240777.8810000005</v>
       </c>
       <c r="E306">
-        <f t="shared" si="4"/>
-        <v>22.407778810000003</v>
+        <v>124.95866000000001</v>
       </c>
     </row>
     <row r="307" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="B307">
         <v>15.143000000000001</v>
@@ -7442,13 +7147,12 @@
         <v>1785135.8950000007</v>
       </c>
       <c r="E307">
-        <f t="shared" si="4"/>
-        <v>17.851358950000009</v>
+        <v>106.62220000000001</v>
       </c>
     </row>
     <row r="308" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="B308">
         <v>16.687000000000001</v>
@@ -7460,13 +7164,12 @@
         <v>758128.63749999995</v>
       </c>
       <c r="E308">
-        <f t="shared" si="4"/>
-        <v>7.5812863749999995</v>
+        <v>37.929079999999999</v>
       </c>
     </row>
     <row r="309" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="B309">
         <v>19.088999999999999</v>
@@ -7478,13 +7181,12 @@
         <v>2097275.8875000011</v>
       </c>
       <c r="E309">
-        <f t="shared" si="4"/>
-        <v>20.972758875000011</v>
+        <v>76.791819999999987</v>
       </c>
     </row>
     <row r="310" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="B310">
         <v>16.196999999999999</v>
@@ -7496,13 +7198,12 @@
         <v>1271026.4500000007</v>
       </c>
       <c r="E310">
-        <f t="shared" si="4"/>
-        <v>12.710264500000006</v>
+        <v>47.359680000000004</v>
       </c>
     </row>
     <row r="311" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="B311">
         <v>16.698</v>
@@ -7514,13 +7215,12 @@
         <v>3441223.7445000014</v>
       </c>
       <c r="E311">
-        <f t="shared" si="4"/>
-        <v>34.412237445000017</v>
+        <v>153.85137999999998</v>
       </c>
     </row>
     <row r="312" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="B312">
         <v>17.661999999999999</v>
@@ -7532,13 +7232,12 @@
         <v>3528232.9955000002</v>
       </c>
       <c r="E312">
-        <f t="shared" si="4"/>
-        <v>35.282329955000002</v>
+        <v>178.52940000000001</v>
       </c>
     </row>
     <row r="313" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="B313">
         <v>16.855</v>
@@ -7550,13 +7249,12 @@
         <v>3162314.7950000013</v>
       </c>
       <c r="E313">
-        <f t="shared" si="4"/>
-        <v>31.623147950000014</v>
+        <v>138.31129999999999</v>
       </c>
     </row>
     <row r="314" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="B314">
         <v>17.687999999999999</v>
@@ -7568,13 +7266,12 @@
         <v>3490977.410000002</v>
       </c>
       <c r="E314">
-        <f t="shared" si="4"/>
-        <v>34.909774100000021</v>
+        <v>148.35608000000002</v>
       </c>
     </row>
     <row r="315" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="B315">
         <v>18.158000000000001</v>
@@ -7586,13 +7283,12 @@
         <v>2732812.4915000009</v>
       </c>
       <c r="E315">
-        <f t="shared" si="4"/>
-        <v>27.328124915000011</v>
+        <v>137.84591999999998</v>
       </c>
     </row>
     <row r="316" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="B316">
         <v>17.007000000000001</v>
@@ -7604,13 +7300,12 @@
         <v>1857176.0225</v>
       </c>
       <c r="E316">
-        <f t="shared" si="4"/>
-        <v>18.571760224999998</v>
+        <v>71.190140000000014</v>
       </c>
     </row>
     <row r="317" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="B317">
         <v>17.273</v>
@@ -7622,13 +7317,12 @@
         <v>2405464.259000001</v>
       </c>
       <c r="E317">
-        <f t="shared" si="4"/>
-        <v>24.054642590000011</v>
+        <v>106.50235999999997</v>
       </c>
     </row>
     <row r="318" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="B318">
         <v>16.692</v>
@@ -7640,13 +7334,12 @@
         <v>2330755.2210000008</v>
       </c>
       <c r="E318">
-        <f t="shared" si="4"/>
-        <v>23.307552210000008</v>
+        <v>97.771339999999995</v>
       </c>
     </row>
     <row r="319" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="B319">
         <v>16.972999999999999</v>
@@ -7658,13 +7351,12 @@
         <v>2455062.3600000013</v>
       </c>
       <c r="E319">
-        <f t="shared" si="4"/>
-        <v>24.550623600000012</v>
+        <v>80.687439999999981</v>
       </c>
     </row>
     <row r="320" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="B320">
         <v>18.108000000000001</v>
@@ -7676,13 +7368,12 @@
         <v>2290675.9000000008</v>
       </c>
       <c r="E320">
-        <f t="shared" si="4"/>
-        <v>22.906759000000008</v>
+        <v>92.23769999999999</v>
       </c>
     </row>
     <row r="321" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="B321">
         <v>17.744</v>
@@ -7694,13 +7385,12 @@
         <v>2470157.0100000012</v>
       </c>
       <c r="E321">
-        <f t="shared" si="4"/>
-        <v>24.701570100000012</v>
+        <v>111.78280000000002</v>
       </c>
     </row>
     <row r="322" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="B322">
         <v>16.991</v>
@@ -7712,13 +7402,12 @@
         <v>2967703.9899999998</v>
       </c>
       <c r="E322">
-        <f t="shared" si="4"/>
-        <v>29.677039899999997</v>
+        <v>120.6901</v>
       </c>
     </row>
     <row r="323" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="B323">
         <v>15.151999999999999</v>
@@ -7730,13 +7419,12 @@
         <v>2942063.3200000008</v>
       </c>
       <c r="E323">
-        <f t="shared" ref="E323:E386" si="5">D323/100000</f>
-        <v>29.420633200000008</v>
+        <v>51.754800000000003</v>
       </c>
     </row>
     <row r="324" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="B324">
         <v>16.847999999999999</v>
@@ -7748,13 +7436,12 @@
         <v>2843065.247500001</v>
       </c>
       <c r="E324">
-        <f t="shared" si="5"/>
-        <v>28.430652475000009</v>
+        <v>162.11431999999996</v>
       </c>
     </row>
     <row r="325" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="B325">
         <v>17.521000000000001</v>
@@ -7766,13 +7453,12 @@
         <v>1921254.8300000008</v>
       </c>
       <c r="E325">
-        <f t="shared" si="5"/>
-        <v>19.212548300000009</v>
+        <v>70.438339999999997</v>
       </c>
     </row>
     <row r="326" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="B326">
         <v>16.832000000000001</v>
@@ -7784,13 +7470,12 @@
         <v>2321428.8400000012</v>
       </c>
       <c r="E326">
-        <f t="shared" si="5"/>
-        <v>23.214288400000012</v>
+        <v>97.173180000000002</v>
       </c>
     </row>
     <row r="327" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="B327">
         <v>17.742999999999999</v>
@@ -7802,13 +7487,12 @@
         <v>2136604.9850000003</v>
       </c>
       <c r="E327">
-        <f t="shared" si="5"/>
-        <v>21.366049850000003</v>
+        <v>96.649259999999998</v>
       </c>
     </row>
     <row r="328" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="B328">
         <v>17.802</v>
@@ -7820,13 +7504,12 @@
         <v>3213855.0700000017</v>
       </c>
       <c r="E328">
-        <f t="shared" si="5"/>
-        <v>32.138550700000017</v>
+        <v>136.70414</v>
       </c>
     </row>
     <row r="329" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="B329">
         <v>15.172000000000001</v>
@@ -7838,13 +7521,12 @@
         <v>1617461.7750000006</v>
       </c>
       <c r="E329">
-        <f t="shared" si="5"/>
-        <v>16.174617750000007</v>
+        <v>55.983899999999991</v>
       </c>
     </row>
     <row r="330" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="B330">
         <v>15.438000000000001</v>
@@ -7856,13 +7538,12 @@
         <v>1467113.0700000003</v>
       </c>
       <c r="E330">
-        <f t="shared" si="5"/>
-        <v>14.671130700000003</v>
+        <v>57.27579999999999</v>
       </c>
     </row>
     <row r="331" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="B331">
         <v>17.684000000000001</v>
@@ -7874,13 +7555,12 @@
         <v>2293216.0700000012</v>
       </c>
       <c r="E331">
-        <f t="shared" si="5"/>
-        <v>22.932160700000011</v>
+        <v>100.51813999999999</v>
       </c>
     </row>
     <row r="332" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="B332">
         <v>18.295999999999999</v>
@@ -7892,13 +7572,12 @@
         <v>2137098.6800000006</v>
       </c>
       <c r="E332">
-        <f t="shared" si="5"/>
-        <v>21.370986800000008</v>
+        <v>72.68213999999999</v>
       </c>
     </row>
     <row r="333" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="B333">
         <v>17.684999999999999</v>
@@ -7910,13 +7589,12 @@
         <v>1340941.6800000004</v>
       </c>
       <c r="E333">
-        <f t="shared" si="5"/>
-        <v>13.409416800000004</v>
+        <v>53.007240000000003</v>
       </c>
     </row>
     <row r="334" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="B334">
         <v>17.672999999999998</v>
@@ -7928,13 +7606,12 @@
         <v>1394611.6100000003</v>
       </c>
       <c r="E334">
-        <f t="shared" si="5"/>
-        <v>13.946116100000003</v>
+        <v>84.780780000000007</v>
       </c>
     </row>
     <row r="335" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="B335">
         <v>16.175000000000001</v>
@@ -7946,13 +7623,12 @@
         <v>2002785.9500000014</v>
       </c>
       <c r="E335">
-        <f t="shared" si="5"/>
-        <v>20.027859500000012</v>
+        <v>97.366839999999968</v>
       </c>
     </row>
     <row r="336" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="B336">
         <v>18.219000000000001</v>
@@ -7964,13 +7640,12 @@
         <v>1675167.8280000004</v>
       </c>
       <c r="E336">
-        <f t="shared" si="5"/>
-        <v>16.751678280000004</v>
+        <v>81.07180000000001</v>
       </c>
     </row>
     <row r="337" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="B337">
         <v>17.047999999999998</v>
@@ -7982,13 +7657,12 @@
         <v>1390496.7600000002</v>
       </c>
       <c r="E337">
-        <f t="shared" si="5"/>
-        <v>13.904967600000003</v>
+        <v>51.876299999999993</v>
       </c>
     </row>
     <row r="338" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="B338">
         <v>20.343</v>
@@ -8000,13 +7674,12 @@
         <v>3087443.5033000014</v>
       </c>
       <c r="E338">
-        <f t="shared" si="5"/>
-        <v>30.874435033000015</v>
+        <v>164.81286</v>
       </c>
     </row>
     <row r="339" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="B339">
         <v>25.010999999999999</v>
@@ -8018,13 +7691,12 @@
         <v>2623549.4349999996</v>
       </c>
       <c r="E339">
-        <f t="shared" si="5"/>
-        <v>26.235494349999996</v>
+        <v>137.11044000000001</v>
       </c>
     </row>
     <row r="340" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="B340">
         <v>20.268999999999998</v>
@@ -8036,13 +7708,12 @@
         <v>2059868.0850000002</v>
       </c>
       <c r="E340">
-        <f t="shared" si="5"/>
-        <v>20.598680850000001</v>
+        <v>105.60097665000001</v>
       </c>
     </row>
     <row r="341" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="B341">
         <v>20.468</v>
@@ -8054,13 +7725,12 @@
         <v>1770315.9780000001</v>
       </c>
       <c r="E341">
-        <f t="shared" si="5"/>
-        <v>17.70315978</v>
+        <v>85.304479650000005</v>
       </c>
     </row>
     <row r="342" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="B342">
         <v>21.494</v>
@@ -8072,13 +7742,12 @@
         <v>2092720.7400000009</v>
       </c>
       <c r="E342">
-        <f t="shared" si="5"/>
-        <v>20.927207400000007</v>
+        <v>105.13692000000002</v>
       </c>
     </row>
     <row r="343" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="B343">
         <v>20.298999999999999</v>
@@ -8090,13 +7759,12 @@
         <v>2426952.1970000016</v>
       </c>
       <c r="E343">
-        <f t="shared" si="5"/>
-        <v>24.269521970000017</v>
+        <v>119.39315504999999</v>
       </c>
     </row>
     <row r="344" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="B344">
         <v>21.870999999999999</v>
@@ -8108,13 +7776,12 @@
         <v>2532936.2045</v>
       </c>
       <c r="E344">
-        <f t="shared" si="5"/>
-        <v>25.329362045</v>
+        <v>135.2097</v>
       </c>
     </row>
     <row r="345" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="B345">
         <v>20.286000000000001</v>
@@ -8126,13 +7793,12 @@
         <v>2129516.1500000004</v>
       </c>
       <c r="E345">
-        <f t="shared" si="5"/>
-        <v>21.295161500000003</v>
+        <v>103.22248949999999</v>
       </c>
     </row>
     <row r="346" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="B346">
         <v>20.323</v>
@@ -8144,13 +7810,12 @@
         <v>1849434.6325000008</v>
       </c>
       <c r="E346">
-        <f t="shared" si="5"/>
-        <v>18.494346325000009</v>
+        <v>105.68844000000001</v>
       </c>
     </row>
     <row r="347" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="B347">
         <v>20.375</v>
@@ -8162,13 +7827,12 @@
         <v>2021661.2675000001</v>
       </c>
       <c r="E347">
-        <f t="shared" si="5"/>
-        <v>20.216612675</v>
+        <v>92.92085999999999</v>
       </c>
     </row>
     <row r="348" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="B348">
         <v>20.234999999999999</v>
@@ -8180,13 +7844,12 @@
         <v>2126051.2800000003</v>
       </c>
       <c r="E348">
-        <f t="shared" si="5"/>
-        <v>21.260512800000004</v>
+        <v>105.61471439999998</v>
       </c>
     </row>
     <row r="349" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A349" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="B349">
         <v>22.253</v>
@@ -8198,13 +7861,12 @@
         <v>1650176.3000000003</v>
       </c>
       <c r="E349">
-        <f t="shared" si="5"/>
-        <v>16.501763000000004</v>
+        <v>96.36005999999999</v>
       </c>
     </row>
     <row r="350" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="B350">
         <v>24.995000000000001</v>
@@ -8216,13 +7878,12 @@
         <v>1490258.2900000003</v>
       </c>
       <c r="E350">
-        <f t="shared" si="5"/>
-        <v>14.902582900000002</v>
+        <v>81.906359999999978</v>
       </c>
     </row>
     <row r="351" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="B351">
         <v>20.481000000000002</v>
@@ -8234,13 +7895,12 @@
         <v>1772852.6600000001</v>
       </c>
       <c r="E351">
-        <f t="shared" si="5"/>
-        <v>17.728526600000002</v>
+        <v>103.29377999999998</v>
       </c>
     </row>
     <row r="352" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A352" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="B352">
         <v>22.242999999999999</v>
@@ -8252,13 +7912,12 @@
         <v>1519209.9725000006</v>
       </c>
       <c r="E352">
-        <f t="shared" si="5"/>
-        <v>15.192099725000006</v>
+        <v>69.664140000000003</v>
       </c>
     </row>
     <row r="353" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A353" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="B353">
         <v>20.256</v>
@@ -8270,13 +7929,12 @@
         <v>2889586.3500000024</v>
       </c>
       <c r="E353">
-        <f t="shared" si="5"/>
-        <v>28.895863500000026</v>
+        <v>133.07975999999999</v>
       </c>
     </row>
     <row r="354" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A354" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="B354">
         <v>20.838000000000001</v>
@@ -8288,13 +7946,12 @@
         <v>1999079.31</v>
       </c>
       <c r="E354">
-        <f t="shared" si="5"/>
-        <v>19.990793100000001</v>
+        <v>99.532259999999994</v>
       </c>
     </row>
     <row r="355" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A355" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="B355">
         <v>19.805</v>
@@ -8306,13 +7963,12 @@
         <v>4033521.8900000034</v>
       </c>
       <c r="E355">
-        <f t="shared" si="5"/>
-        <v>40.335218900000037</v>
+        <v>174.81366</v>
       </c>
     </row>
     <row r="356" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A356" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="B356">
         <v>22.227</v>
@@ -8324,13 +7980,12 @@
         <v>2273780.9700000011</v>
       </c>
       <c r="E356">
-        <f t="shared" si="5"/>
-        <v>22.73780970000001</v>
+        <v>123.87335999999999</v>
       </c>
     </row>
     <row r="357" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A357" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="B357">
         <v>21.472999999999999</v>
@@ -8342,13 +7997,12 @@
         <v>2678556.9700000011</v>
       </c>
       <c r="E357">
-        <f t="shared" si="5"/>
-        <v>26.785569700000011</v>
+        <v>147.74808000000002</v>
       </c>
     </row>
     <row r="358" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A358" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="B358">
         <v>20.469000000000001</v>
@@ -8360,13 +8014,12 @@
         <v>2876448.3855000013</v>
       </c>
       <c r="E358">
-        <f t="shared" si="5"/>
-        <v>28.764483855000012</v>
+        <v>148.73862</v>
       </c>
     </row>
     <row r="359" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A359" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="B359">
         <v>20.353000000000002</v>
@@ -8378,13 +8031,12 @@
         <v>3985816.9225000022</v>
       </c>
       <c r="E359">
-        <f t="shared" si="5"/>
-        <v>39.858169225000019</v>
+        <v>273.06533999999999</v>
       </c>
     </row>
     <row r="360" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A360" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="B360">
         <v>20.279</v>
@@ -8396,13 +8048,12 @@
         <v>1903732.9200000002</v>
       </c>
       <c r="E360">
-        <f t="shared" si="5"/>
-        <v>19.037329200000002</v>
+        <v>108.07158</v>
       </c>
     </row>
     <row r="361" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A361" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="B361">
         <v>19.314</v>
@@ -8414,13 +8065,12 @@
         <v>3179932.5199999996</v>
       </c>
       <c r="E361">
-        <f t="shared" si="5"/>
-        <v>31.799325199999995</v>
+        <v>154.62947999999997</v>
       </c>
     </row>
     <row r="362" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A362" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="B362">
         <v>20.260999999999999</v>
@@ -8432,13 +8082,12 @@
         <v>2681351.330000001</v>
       </c>
       <c r="E362">
-        <f t="shared" si="5"/>
-        <v>26.813513300000011</v>
+        <v>133.61611575000001</v>
       </c>
     </row>
     <row r="363" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A363" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="B363">
         <v>20.292000000000002</v>
@@ -8450,13 +8099,12 @@
         <v>2675428.0000000014</v>
       </c>
       <c r="E363">
-        <f t="shared" si="5"/>
-        <v>26.754280000000016</v>
+        <v>107.27940000000001</v>
       </c>
     </row>
     <row r="364" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A364" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="B364">
         <v>20.241</v>
@@ -8468,13 +8116,12 @@
         <v>1881320.3960000011</v>
       </c>
       <c r="E364">
-        <f t="shared" si="5"/>
-        <v>18.81320396000001</v>
+        <v>90.890039999999999</v>
       </c>
     </row>
     <row r="365" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A365" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="B365">
         <v>20.279</v>
@@ -8486,13 +8133,12 @@
         <v>981031.94500000007</v>
       </c>
       <c r="E365">
-        <f t="shared" si="5"/>
-        <v>9.8103194500000015</v>
+        <v>65.397059999999996</v>
       </c>
     </row>
     <row r="366" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A366" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="B366">
         <v>22.254000000000001</v>
@@ -8504,13 +8150,12 @@
         <v>1483013.48</v>
       </c>
       <c r="E366">
-        <f t="shared" si="5"/>
-        <v>14.8301348</v>
+        <v>93.906060000000025</v>
       </c>
     </row>
     <row r="367" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A367" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="B367">
         <v>25.629000000000001</v>
@@ -8522,13 +8167,12 @@
         <v>1469104.9875</v>
       </c>
       <c r="E367">
-        <f t="shared" si="5"/>
-        <v>14.691049875000001</v>
+        <v>102.00029999999998</v>
       </c>
     </row>
     <row r="368" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A368" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="B368">
         <v>20.148</v>
@@ -8540,13 +8184,12 @@
         <v>1270001.2244999998</v>
       </c>
       <c r="E368">
-        <f t="shared" si="5"/>
-        <v>12.700012244999998</v>
+        <v>69.349799999999988</v>
       </c>
     </row>
     <row r="369" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A369" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="B369">
         <v>32.933</v>
@@ -8558,13 +8201,12 @@
         <v>3367278.9350000024</v>
       </c>
       <c r="E369">
-        <f t="shared" si="5"/>
-        <v>33.672789350000023</v>
+        <v>147.48796145999998</v>
       </c>
     </row>
     <row r="370" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A370" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="B370">
         <v>32.741999999999997</v>
@@ -8576,13 +8218,12 @@
         <v>2371927.8800000013</v>
       </c>
       <c r="E370">
-        <f t="shared" si="5"/>
-        <v>23.719278800000012</v>
+        <v>81.626452599999993</v>
       </c>
     </row>
     <row r="371" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A371" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="B371">
         <v>29.609000000000002</v>
@@ -8594,13 +8235,12 @@
         <v>2320542.52</v>
       </c>
       <c r="E371">
-        <f t="shared" si="5"/>
-        <v>23.205425200000001</v>
+        <v>125.71257630000001</v>
       </c>
     </row>
     <row r="372" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A372" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="B372">
         <v>34.031999999999996</v>
@@ -8612,13 +8252,12 @@
         <v>2139974.9600000004</v>
       </c>
       <c r="E372">
-        <f t="shared" si="5"/>
-        <v>21.399749600000003</v>
+        <v>118.30654686000003</v>
       </c>
     </row>
     <row r="373" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A373" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="B373">
         <v>32.984999999999999</v>
@@ -8630,13 +8269,12 @@
         <v>885512.66000000015</v>
       </c>
       <c r="E373">
-        <f t="shared" si="5"/>
-        <v>8.855126600000002</v>
+        <v>46.799293399999996</v>
       </c>
     </row>
     <row r="374" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A374" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="B374">
         <v>33.027000000000001</v>
@@ -8647,14 +8285,13 @@
       <c r="D374">
         <v>3390955.100000001</v>
       </c>
-      <c r="E374">
-        <f t="shared" si="5"/>
-        <v>33.909551000000008</v>
+      <c r="E374" s="2">
+        <v>135.63820400000003</v>
       </c>
     </row>
     <row r="375" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A375" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="B375">
         <v>32.743000000000002</v>
@@ -8666,13 +8303,12 @@
         <v>2223942.2115000002</v>
       </c>
       <c r="E375">
-        <f t="shared" si="5"/>
-        <v>22.239422115000004</v>
+        <v>82.865985699999996</v>
       </c>
     </row>
     <row r="376" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A376" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="B376">
         <v>32.703000000000003</v>
@@ -8684,13 +8320,12 @@
         <v>2546442.7700000009</v>
       </c>
       <c r="E376">
-        <f t="shared" si="5"/>
-        <v>25.464427700000009</v>
+        <v>105.553257</v>
       </c>
     </row>
     <row r="377" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A377" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="B377">
         <v>34.076000000000001</v>
@@ -8702,13 +8337,12 @@
         <v>1041121.1100000003</v>
       </c>
       <c r="E377">
-        <f t="shared" si="5"/>
-        <v>10.411211100000003</v>
+        <v>71.353512959999989</v>
       </c>
     </row>
     <row r="378" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A378" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="B378">
         <v>34.063000000000002</v>
@@ -8720,13 +8354,12 @@
         <v>1349453.5000000005</v>
       </c>
       <c r="E378">
-        <f t="shared" si="5"/>
-        <v>13.494535000000004</v>
+        <v>102.73411211999999</v>
       </c>
     </row>
     <row r="379" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A379" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="B379">
         <v>32.743000000000002</v>
@@ -8738,13 +8371,12 @@
         <v>3364702.3900000025</v>
       </c>
       <c r="E379">
-        <f t="shared" si="5"/>
-        <v>33.647023900000022</v>
+        <v>128.59710560000002</v>
       </c>
     </row>
     <row r="380" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A380" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="B380">
         <v>33.738999999999997</v>
@@ -8756,13 +8388,12 @@
         <v>957542.08000000019</v>
       </c>
       <c r="E380">
-        <f t="shared" si="5"/>
-        <v>9.5754208000000016</v>
+        <v>62.780450639999991</v>
       </c>
     </row>
     <row r="381" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A381" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="B381">
         <v>29.922000000000001</v>
@@ -8774,13 +8405,12 @@
         <v>1832423.3200000008</v>
       </c>
       <c r="E381">
-        <f t="shared" si="5"/>
-        <v>18.324233200000009</v>
+        <v>109.3731514</v>
       </c>
     </row>
     <row r="382" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A382" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="B382">
         <v>32.723999999999997</v>
@@ -8792,13 +8422,12 @@
         <v>2827458.4625000032</v>
       </c>
       <c r="E382">
-        <f t="shared" si="5"/>
-        <v>28.274584625000031</v>
+        <v>119.1499458</v>
       </c>
     </row>
     <row r="383" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A383" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="B383">
         <v>32.704999999999998</v>
@@ -8810,13 +8439,12 @@
         <v>5139214.0850000065</v>
       </c>
       <c r="E383">
-        <f t="shared" si="5"/>
-        <v>51.392140850000068</v>
+        <v>213.55516450000002</v>
       </c>
     </row>
     <row r="384" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A384" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="B384">
         <v>32.726999999999997</v>
@@ -8828,13 +8456,12 @@
         <v>3825880.3100000042</v>
       </c>
       <c r="E384">
-        <f t="shared" si="5"/>
-        <v>38.258803100000044</v>
+        <v>187.08763490000001</v>
       </c>
     </row>
     <row r="385" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A385" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="B385">
         <v>32.99</v>
@@ -8846,13 +8473,12 @@
         <v>3912698.9000000055</v>
       </c>
       <c r="E385">
-        <f t="shared" si="5"/>
-        <v>39.126989000000052</v>
+        <v>149.1235557</v>
       </c>
     </row>
     <row r="386" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A386" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="B386">
         <v>29.905999999999999</v>
@@ -8864,13 +8490,12 @@
         <v>2805363.8350000023</v>
       </c>
       <c r="E386">
-        <f t="shared" si="5"/>
-        <v>28.053638350000021</v>
+        <v>170.141426</v>
       </c>
     </row>
     <row r="387" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A387" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="B387">
         <v>32.764000000000003</v>
@@ -8882,13 +8507,12 @@
         <v>4522032.5250000032</v>
       </c>
       <c r="E387">
-        <f t="shared" ref="E387:E450" si="6">D387/100000</f>
-        <v>45.22032525000003</v>
+        <v>168.95234299999998</v>
       </c>
     </row>
     <row r="388" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A388" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B388">
         <v>32.668999999999997</v>
@@ -8900,13 +8524,12 @@
         <v>2845156.6700000023</v>
       </c>
       <c r="E388">
-        <f t="shared" si="6"/>
-        <v>28.451566700000022</v>
+        <v>107.310147</v>
       </c>
     </row>
     <row r="389" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A389" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="B389">
         <v>32.67</v>
@@ -8918,13 +8541,12 @@
         <v>2288790.0300000017</v>
       </c>
       <c r="E389">
-        <f t="shared" si="6"/>
-        <v>22.887900300000016</v>
+        <v>111.30210099999999</v>
       </c>
     </row>
     <row r="390" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A390" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="B390">
         <v>32.76</v>
@@ -8936,13 +8558,12 @@
         <v>2041466.8800000011</v>
       </c>
       <c r="E390">
-        <f t="shared" si="6"/>
-        <v>20.414668800000012</v>
+        <v>77.233643699999988</v>
       </c>
     </row>
     <row r="391" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A391" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="B391">
         <v>34.262999999999998</v>
@@ -8954,13 +8575,12 @@
         <v>905124.00999999989</v>
       </c>
       <c r="E391">
-        <f t="shared" si="6"/>
-        <v>9.0512400999999993</v>
+        <v>53.221124519999989</v>
       </c>
     </row>
     <row r="392" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A392" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="B392">
         <v>32.688000000000002</v>
@@ -8972,13 +8592,12 @@
         <v>2371243.4500000016</v>
       </c>
       <c r="E392">
-        <f t="shared" si="6"/>
-        <v>23.712434500000015</v>
+        <v>110.91594850000001</v>
       </c>
     </row>
     <row r="393" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A393" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="B393">
         <v>34.103000000000002</v>
@@ -8990,13 +8609,12 @@
         <v>1850655.0300000007</v>
       </c>
       <c r="E393">
-        <f t="shared" si="6"/>
-        <v>18.506550300000008</v>
+        <v>95.376926820000008</v>
       </c>
     </row>
     <row r="394" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A394" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="B394">
         <v>32.645000000000003</v>
@@ -9008,13 +8626,12 @@
         <v>1735844.4000000006</v>
       </c>
       <c r="E394">
-        <f t="shared" si="6"/>
-        <v>17.358444000000006</v>
+        <v>54.185311799999994</v>
       </c>
     </row>
     <row r="395" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A395" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="B395">
         <v>32.567</v>
@@ -9026,13 +8643,12 @@
         <v>2873970.4100000029</v>
       </c>
       <c r="E395">
-        <f t="shared" si="6"/>
-        <v>28.739704100000029</v>
+        <v>111.94132279999999</v>
       </c>
     </row>
     <row r="396" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A396" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="B396">
         <v>22.43</v>
@@ -9044,13 +8660,12 @@
         <v>844086.03</v>
       </c>
       <c r="E396">
-        <f t="shared" si="6"/>
-        <v>8.4408603000000006</v>
+        <v>38.275940000000006</v>
       </c>
     </row>
     <row r="397" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A397" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B397">
         <v>19.867000000000001</v>
@@ -9062,13 +8677,12 @@
         <v>2322555.6140000015</v>
       </c>
       <c r="E397">
-        <f t="shared" si="6"/>
-        <v>23.225556140000016</v>
+        <v>120.77988999999999</v>
       </c>
     </row>
     <row r="398" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A398" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="B398">
         <v>18.981999999999999</v>
@@ -9080,13 +8694,12 @@
         <v>1773783.1815000009</v>
       </c>
       <c r="E398">
-        <f t="shared" si="6"/>
-        <v>17.73783181500001</v>
+        <v>88.731399999999994</v>
       </c>
     </row>
     <row r="399" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A399" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="B399">
         <v>23.077000000000002</v>
@@ -9098,13 +8711,12 @@
         <v>3406740.0790000032</v>
       </c>
       <c r="E399">
-        <f t="shared" si="6"/>
-        <v>34.067400790000029</v>
+        <v>161.85019</v>
       </c>
     </row>
     <row r="400" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A400" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="B400">
         <v>19.847999999999999</v>
@@ -9116,13 +8728,12 @@
         <v>1016728.6584999999</v>
       </c>
       <c r="E400">
-        <f t="shared" si="6"/>
-        <v>10.167286584999999</v>
+        <v>27.364989999999999</v>
       </c>
     </row>
     <row r="401" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A401" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="B401">
         <v>19.876000000000001</v>
@@ -9134,13 +8745,12 @@
         <v>2341837.1240000003</v>
       </c>
       <c r="E401">
-        <f t="shared" si="6"/>
-        <v>23.418371240000003</v>
+        <v>116.77226999999999</v>
       </c>
     </row>
     <row r="402" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A402" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="B402">
         <v>21.013999999999999</v>
@@ -9152,13 +8762,12 @@
         <v>1563825.0859999999</v>
       </c>
       <c r="E402">
-        <f t="shared" si="6"/>
-        <v>15.638250859999999</v>
+        <v>75.025677819999999</v>
       </c>
     </row>
     <row r="403" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A403" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="B403">
         <v>19.914000000000001</v>
@@ -9170,13 +8779,12 @@
         <v>1160600.0614999998</v>
       </c>
       <c r="E403">
-        <f t="shared" si="6"/>
-        <v>11.606000614999999</v>
+        <v>59.455150000000003</v>
       </c>
     </row>
     <row r="404" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A404" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="B404">
         <v>21.041</v>
@@ -9188,13 +8796,12 @@
         <v>2720961.3132999996</v>
       </c>
       <c r="E404">
-        <f t="shared" si="6"/>
-        <v>27.209613132999994</v>
+        <v>126.89930722999999</v>
       </c>
     </row>
     <row r="405" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A405" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="B405">
         <v>22.463000000000001</v>
@@ -9206,13 +8813,12 @@
         <v>3797680.6755000027</v>
       </c>
       <c r="E405">
-        <f t="shared" si="6"/>
-        <v>37.976806755000027</v>
+        <v>186.60780999999997</v>
       </c>
     </row>
     <row r="406" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A406" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="B406">
         <v>21.641999999999999</v>
@@ -9224,13 +8830,12 @@
         <v>2471004.2950000009</v>
       </c>
       <c r="E406">
-        <f t="shared" si="6"/>
-        <v>24.710042950000009</v>
+        <v>118.61613</v>
       </c>
     </row>
     <row r="407" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A407" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="B407">
         <v>19.876000000000001</v>
@@ -9242,13 +8847,12 @@
         <v>2082181.3580000007</v>
       </c>
       <c r="E407">
-        <f t="shared" si="6"/>
-        <v>20.821813580000008</v>
+        <v>99.670669999999973</v>
       </c>
     </row>
     <row r="408" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A408" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="B408">
         <v>23.065999999999999</v>
@@ -9260,13 +8864,12 @@
         <v>3301054.9250000026</v>
       </c>
       <c r="E408">
-        <f t="shared" si="6"/>
-        <v>33.010549250000025</v>
+        <v>156.26261</v>
       </c>
     </row>
     <row r="409" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A409" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B409">
         <v>21.004000000000001</v>
@@ -9278,13 +8881,12 @@
         <v>4404935.9400000004</v>
       </c>
       <c r="E409">
-        <f t="shared" si="6"/>
-        <v>44.049359400000007</v>
+        <v>221.48973368</v>
       </c>
     </row>
     <row r="410" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A410" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="B410">
         <v>22.484999999999999</v>
@@ -9296,13 +8898,12 @@
         <v>3861630.3555000033</v>
       </c>
       <c r="E410">
-        <f t="shared" si="6"/>
-        <v>38.61630355500003</v>
+        <v>200.46182999999996</v>
       </c>
     </row>
     <row r="411" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A411" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="B411">
         <v>19.876999999999999</v>
@@ -9314,13 +8915,12 @@
         <v>1216311.2200000002</v>
       </c>
       <c r="E411">
-        <f t="shared" si="6"/>
-        <v>12.163112200000002</v>
+        <v>12.82508</v>
       </c>
     </row>
     <row r="412" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A412" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="B412">
         <v>21.510999999999999</v>
@@ -9332,13 +8932,12 @@
         <v>2042378.6510000017</v>
       </c>
       <c r="E412">
-        <f t="shared" si="6"/>
-        <v>20.423786510000017</v>
+        <v>104.69023000000001</v>
       </c>
     </row>
     <row r="413" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A413" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="B413">
         <v>20.914999999999999</v>
@@ -9350,13 +8949,12 @@
         <v>2639104.9155000015</v>
       </c>
       <c r="E413">
-        <f t="shared" si="6"/>
-        <v>26.391049155000015</v>
+        <v>131.63062668000003</v>
       </c>
     </row>
     <row r="414" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A414" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="B414">
         <v>23.239000000000001</v>
@@ -9368,13 +8966,12 @@
         <v>3033895.1600000025</v>
       </c>
       <c r="E414">
-        <f t="shared" si="6"/>
-        <v>30.338951600000026</v>
+        <v>136.36786999999998</v>
       </c>
     </row>
     <row r="415" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A415" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="B415">
         <v>20.928999999999998</v>
@@ -9386,13 +8983,12 @@
         <v>1342677.6270000006</v>
       </c>
       <c r="E415">
-        <f t="shared" si="6"/>
-        <v>13.426776270000005</v>
+        <v>57.315820000000002</v>
       </c>
     </row>
     <row r="416" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A416" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="B416">
         <v>21.521000000000001</v>
@@ -9404,13 +9000,12 @@
         <v>1214965.6600000001</v>
       </c>
       <c r="E416">
-        <f t="shared" si="6"/>
-        <v>12.149656600000002</v>
+        <v>53.893039999999999</v>
       </c>
     </row>
     <row r="417" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A417" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="B417">
         <v>23.239000000000001</v>
@@ -9422,13 +9017,12 @@
         <v>1632371.6300000011</v>
       </c>
       <c r="E417">
-        <f t="shared" si="6"/>
-        <v>16.323716300000012</v>
+        <v>65.845459999999989</v>
       </c>
     </row>
     <row r="418" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A418" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="B418">
         <v>21.196999999999999</v>
@@ -9440,13 +9034,12 @@
         <v>1275344.0774999999</v>
       </c>
       <c r="E418">
-        <f t="shared" si="6"/>
-        <v>12.753440775</v>
+        <v>44.691239999999993</v>
       </c>
     </row>
     <row r="419" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A419" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="B419">
         <v>22.623999999999999</v>
@@ -9458,13 +9051,12 @@
         <v>634119.74999999977</v>
       </c>
       <c r="E419">
-        <f t="shared" si="6"/>
-        <v>6.341197499999998</v>
+        <v>26.447150000000001</v>
       </c>
     </row>
     <row r="420" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A420" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="B420">
         <v>21.239000000000001</v>
@@ -9476,13 +9068,12 @@
         <v>1031505.0600000003</v>
       </c>
       <c r="E420">
-        <f t="shared" si="6"/>
-        <v>10.315050600000003</v>
+        <v>30.979990000000001</v>
       </c>
     </row>
     <row r="421" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A421" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="B421">
         <v>21.116</v>
@@ -9494,13 +9085,12 @@
         <v>922642.71000000008</v>
       </c>
       <c r="E421">
-        <f t="shared" si="6"/>
-        <v>9.2264271000000004</v>
+        <v>38.678519999999999</v>
       </c>
     </row>
     <row r="422" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A422" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B422">
         <v>21.276</v>
@@ -9512,13 +9102,12 @@
         <v>545074.11999999988</v>
       </c>
       <c r="E422">
-        <f t="shared" si="6"/>
-        <v>5.4507411999999986</v>
+        <v>22.789170000000002</v>
       </c>
     </row>
     <row r="423" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A423" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="B423">
         <v>22.521999999999998</v>
@@ -9530,13 +9119,12 @@
         <v>811226.90000000026</v>
       </c>
       <c r="E423">
-        <f t="shared" si="6"/>
-        <v>8.1122690000000031</v>
+        <v>35.231070549999998</v>
       </c>
     </row>
     <row r="424" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A424" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="B424">
         <v>21.256</v>
@@ -9548,13 +9136,12 @@
         <v>2614906.1907000006</v>
       </c>
       <c r="E424">
-        <f t="shared" si="6"/>
-        <v>26.149061907000007</v>
+        <v>125.73253000000003</v>
       </c>
     </row>
     <row r="425" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A425" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="B425">
         <v>23.172000000000001</v>
@@ -9566,13 +9153,12 @@
         <v>2536014.7775000008</v>
       </c>
       <c r="E425">
-        <f t="shared" si="6"/>
-        <v>25.360147775000009</v>
+        <v>130.00548580999998</v>
       </c>
     </row>
     <row r="426" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A426" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="B426">
         <v>22.097999999999999</v>
@@ -9584,13 +9170,12 @@
         <v>2388020.3050000002</v>
       </c>
       <c r="E426">
-        <f t="shared" si="6"/>
-        <v>23.880203050000002</v>
+        <v>144.26477</v>
       </c>
     </row>
     <row r="427" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A427" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="B427">
         <v>21.236999999999998</v>
@@ -9602,13 +9187,12 @@
         <v>2184359.0440000007</v>
       </c>
       <c r="E427">
-        <f t="shared" si="6"/>
-        <v>21.843590440000007</v>
+        <v>109.89436000000001</v>
       </c>
     </row>
     <row r="428" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A428" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="B428">
         <v>23.23</v>
@@ -9620,13 +9204,12 @@
         <v>1911937.5875000001</v>
       </c>
       <c r="E428">
-        <f t="shared" si="6"/>
-        <v>19.119375875000003</v>
+        <v>108.37224000000001</v>
       </c>
     </row>
     <row r="429" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A429" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="B429">
         <v>22.771999999999998</v>
@@ -9638,13 +9221,12 @@
         <v>2440277.9045000011</v>
       </c>
       <c r="E429">
-        <f t="shared" si="6"/>
-        <v>24.40277904500001</v>
+        <v>120.83489912999997</v>
       </c>
     </row>
     <row r="430" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A430" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="B430">
         <v>22.716999999999999</v>
@@ -9656,13 +9238,12 @@
         <v>2204281.3205000008</v>
       </c>
       <c r="E430">
-        <f t="shared" si="6"/>
-        <v>22.042813205000009</v>
+        <v>98.413550000000015</v>
       </c>
     </row>
     <row r="431" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A431" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="B431">
         <v>23.181000000000001</v>
@@ -9674,13 +9255,12 @@
         <v>4040775.3545000008</v>
       </c>
       <c r="E431">
-        <f t="shared" si="6"/>
-        <v>40.407753545000006</v>
+        <v>192.78007139000002</v>
       </c>
     </row>
     <row r="432" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A432" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="B432">
         <v>19.254000000000001</v>
@@ -9692,13 +9272,12 @@
         <v>1689274.9800000011</v>
       </c>
       <c r="E432">
-        <f t="shared" si="6"/>
-        <v>16.892749800000011</v>
+        <v>49.8474</v>
       </c>
     </row>
     <row r="433" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A433" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="B433">
         <v>23.119</v>
@@ -9710,13 +9289,12 @@
         <v>1433551.7389999998</v>
       </c>
       <c r="E433">
-        <f t="shared" si="6"/>
-        <v>14.335517389999998</v>
+        <v>56.771371809999977</v>
       </c>
     </row>
     <row r="434" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A434" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="B434">
         <v>22.355</v>
@@ -9728,13 +9306,12 @@
         <v>2844615.9765000017</v>
       </c>
       <c r="E434">
-        <f t="shared" si="6"/>
-        <v>28.446159765000019</v>
+        <v>138.73463000000001</v>
       </c>
     </row>
     <row r="435" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A435" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="B435">
         <v>23.263999999999999</v>
@@ -9746,13 +9323,12 @@
         <v>2076841.3060000013</v>
       </c>
       <c r="E435">
-        <f t="shared" si="6"/>
-        <v>20.768413060000011</v>
+        <v>79.702539999999999</v>
       </c>
     </row>
     <row r="436" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A436" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="B436">
         <v>22.556000000000001</v>
@@ -9764,13 +9340,12 @@
         <v>2050618.0875000008</v>
       </c>
       <c r="E436">
-        <f t="shared" si="6"/>
-        <v>20.506180875000009</v>
+        <v>79.382806329999994</v>
       </c>
     </row>
     <row r="437" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A437" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="B437">
         <v>22.742999999999999</v>
@@ -9782,13 +9357,12 @@
         <v>1114677.0405000001</v>
       </c>
       <c r="E437">
-        <f t="shared" si="6"/>
-        <v>11.146770405000002</v>
+        <v>52.553480000000008</v>
       </c>
     </row>
     <row r="438" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A438" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="B438">
         <v>22.707000000000001</v>
@@ -9800,13 +9374,12 @@
         <v>2193854.747500001</v>
       </c>
       <c r="E438">
-        <f t="shared" si="6"/>
-        <v>21.938547475000011</v>
+        <v>99.505908660000031</v>
       </c>
     </row>
     <row r="439" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A439" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="B439">
         <v>24.54</v>
@@ -9818,13 +9391,12 @@
         <v>1578643.96</v>
       </c>
       <c r="E439">
-        <f t="shared" si="6"/>
-        <v>15.7864396</v>
+        <v>95.54351964</v>
       </c>
     </row>
     <row r="440" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A440" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="B440">
         <v>23.196000000000002</v>
@@ -9836,13 +9408,12 @@
         <v>1724019.1200000006</v>
       </c>
       <c r="E440">
-        <f t="shared" si="6"/>
-        <v>17.240191200000005</v>
+        <v>79.423735060000013</v>
       </c>
     </row>
     <row r="441" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A441" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="B441">
         <v>21.314</v>
@@ -9854,13 +9425,12 @@
         <v>1203341.2900000003</v>
       </c>
       <c r="E441">
-        <f t="shared" si="6"/>
-        <v>12.033412900000002</v>
+        <v>72.215394259999997</v>
       </c>
     </row>
     <row r="442" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A442" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="B442">
         <v>23.521000000000001</v>
@@ -9872,13 +9442,12 @@
         <v>1491008.1600000004</v>
       </c>
       <c r="E442">
-        <f t="shared" si="6"/>
-        <v>14.910081600000003</v>
+        <v>78.731000000000009</v>
       </c>
     </row>
     <row r="443" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A443" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="B443">
         <v>22.747</v>
@@ -9890,13 +9459,12 @@
         <v>1236907.8299999998</v>
       </c>
       <c r="E443">
-        <f t="shared" si="6"/>
-        <v>12.369078299999998</v>
+        <v>49.061750000000011</v>
       </c>
     </row>
     <row r="444" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A444" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="B444">
         <v>21.238</v>
@@ -9908,13 +9476,12 @@
         <v>1726951.9943000006</v>
       </c>
       <c r="E444">
-        <f t="shared" si="6"/>
-        <v>17.269519943000006</v>
+        <v>86.382110000000011</v>
       </c>
     </row>
     <row r="445" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A445" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="B445">
         <v>21.219000000000001</v>
@@ -9926,13 +9493,12 @@
         <v>1640981.4175000004</v>
       </c>
       <c r="E445">
-        <f t="shared" si="6"/>
-        <v>16.409814175000005</v>
+        <v>90.257939999999991</v>
       </c>
     </row>
     <row r="446" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A446" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="B446">
         <v>21.268999999999998</v>
@@ -9944,13 +9510,12 @@
         <v>2956314.3265000028</v>
       </c>
       <c r="E446">
-        <f t="shared" si="6"/>
-        <v>29.563143265000029</v>
+        <v>142.70428999999999</v>
       </c>
     </row>
     <row r="447" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A447" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="B447">
         <v>23.187000000000001</v>
@@ -9962,13 +9527,12 @@
         <v>1854085.5350000001</v>
       </c>
       <c r="E447">
-        <f t="shared" si="6"/>
-        <v>18.540855350000001</v>
+        <v>96.819820000000007</v>
       </c>
     </row>
     <row r="448" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A448" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="B448">
         <v>23.135999999999999</v>
@@ -9980,13 +9544,12 @@
         <v>2314473.9473000015</v>
       </c>
       <c r="E448">
-        <f t="shared" si="6"/>
-        <v>23.144739473000016</v>
+        <v>119.03817194000001</v>
       </c>
     </row>
     <row r="449" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A449" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="B449">
         <v>22.763000000000002</v>
@@ -9998,13 +9561,12 @@
         <v>2108205.1782000014</v>
       </c>
       <c r="E449">
-        <f t="shared" si="6"/>
-        <v>21.082051782000015</v>
+        <v>88.97014999999999</v>
       </c>
     </row>
     <row r="450" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A450" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="B450">
         <v>19.184999999999999</v>
@@ -10016,13 +9578,12 @@
         <v>1847721.8350000004</v>
       </c>
       <c r="E450">
-        <f t="shared" si="6"/>
-        <v>18.477218350000005</v>
+        <v>81.952399999999997</v>
       </c>
     </row>
     <row r="451" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A451" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="B451">
         <v>22.073</v>
@@ -10034,13 +9595,12 @@
         <v>2218358.0795000005</v>
       </c>
       <c r="E451">
-        <f t="shared" ref="E451:E505" si="7">D451/100000</f>
-        <v>22.183580795000005</v>
+        <v>129.72508000000002</v>
       </c>
     </row>
     <row r="452" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A452" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="B452">
         <v>22.704000000000001</v>
@@ -10052,13 +9612,12 @@
         <v>2005536.7725000007</v>
       </c>
       <c r="E452">
-        <f t="shared" si="7"/>
-        <v>20.055367725000007</v>
+        <v>97.629649999999998</v>
       </c>
     </row>
     <row r="453" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A453" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="B453">
         <v>23.119</v>
@@ -10070,13 +9629,12 @@
         <v>2911461.1785000009</v>
       </c>
       <c r="E453">
-        <f t="shared" si="7"/>
-        <v>29.114611785000008</v>
+        <v>137.67474999999999</v>
       </c>
     </row>
     <row r="454" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A454" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="B454">
         <v>23.295999999999999</v>
@@ -10088,13 +9646,12 @@
         <v>1831730.2100000014</v>
       </c>
       <c r="E454">
-        <f t="shared" si="7"/>
-        <v>18.317302100000013</v>
+        <v>91.25033126999999</v>
       </c>
     </row>
     <row r="455" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A455" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="B455">
         <v>22.75</v>
@@ -10106,13 +9663,12 @@
         <v>2892069.1210000021</v>
       </c>
       <c r="E455">
-        <f t="shared" si="7"/>
-        <v>28.920691210000022</v>
+        <v>114.76295</v>
       </c>
     </row>
     <row r="456" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A456" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="B456">
         <v>22.699000000000002</v>
@@ -10124,13 +9680,12 @@
         <v>3794266.9690000042</v>
       </c>
       <c r="E456">
-        <f t="shared" si="7"/>
-        <v>37.942669690000045</v>
+        <v>182.79795222000001</v>
       </c>
     </row>
     <row r="457" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A457" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="B457">
         <v>21.24</v>
@@ -10142,13 +9697,12 @@
         <v>977756.65000000037</v>
       </c>
       <c r="E457">
-        <f t="shared" si="7"/>
-        <v>9.7775665000000043</v>
+        <v>33.446799999999996</v>
       </c>
     </row>
     <row r="458" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A458" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="B458">
         <v>23.123999999999999</v>
@@ -10160,13 +9714,12 @@
         <v>2482872.9620000012</v>
       </c>
       <c r="E458">
-        <f t="shared" si="7"/>
-        <v>24.828729620000011</v>
+        <v>124.24486528</v>
       </c>
     </row>
     <row r="459" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A459" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="B459">
         <v>22.077000000000002</v>
@@ -10178,13 +9731,12 @@
         <v>1777222.7800000007</v>
       </c>
       <c r="E459">
-        <f t="shared" si="7"/>
-        <v>17.772227800000007</v>
+        <v>99.375799999999984</v>
       </c>
     </row>
     <row r="460" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A460" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="B460">
         <v>23.233000000000001</v>
@@ -10196,13 +9748,12 @@
         <v>2597479.1399999997</v>
       </c>
       <c r="E460">
-        <f t="shared" si="7"/>
-        <v>25.974791399999997</v>
+        <v>97.327213409999999</v>
       </c>
     </row>
     <row r="461" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A461" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="B461">
         <v>23.212</v>
@@ -10214,13 +9765,12 @@
         <v>1710562.9962000009</v>
       </c>
       <c r="E461">
-        <f t="shared" si="7"/>
-        <v>17.105629962000009</v>
+        <v>73.079911070000009</v>
       </c>
     </row>
     <row r="462" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A462" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="B462">
         <v>23.157</v>
@@ -10232,13 +9782,12 @@
         <v>2817933.0425000032</v>
       </c>
       <c r="E462">
-        <f t="shared" si="7"/>
-        <v>28.179330425000032</v>
+        <v>130.30602041000003</v>
       </c>
     </row>
     <row r="463" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A463" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="B463">
         <v>22.725000000000001</v>
@@ -10250,13 +9799,12 @@
         <v>3981385.977300005</v>
       </c>
       <c r="E463">
-        <f t="shared" si="7"/>
-        <v>39.813859773000047</v>
+        <v>187.41045625999999</v>
       </c>
     </row>
     <row r="464" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A464" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="B464">
         <v>23.274000000000001</v>
@@ -10268,13 +9816,12 @@
         <v>2684764.7750000018</v>
       </c>
       <c r="E464">
-        <f t="shared" si="7"/>
-        <v>26.847647750000018</v>
+        <v>121.20383000000002</v>
       </c>
     </row>
     <row r="465" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A465" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="B465">
         <v>21.254999999999999</v>
@@ -10286,13 +9833,12 @@
         <v>2353813.0550000016</v>
       </c>
       <c r="E465">
-        <f t="shared" si="7"/>
-        <v>23.538130550000016</v>
+        <v>97.371480000000005</v>
       </c>
     </row>
     <row r="466" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A466" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="B466">
         <v>22.094000000000001</v>
@@ -10304,13 +9850,12 @@
         <v>2799099.0280000013</v>
       </c>
       <c r="E466">
-        <f t="shared" si="7"/>
-        <v>27.990990280000013</v>
+        <v>130.59379999999999</v>
       </c>
     </row>
     <row r="467" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A467" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="B467">
         <v>22.722000000000001</v>
@@ -10322,13 +9867,12 @@
         <v>1077107.3200000003</v>
       </c>
       <c r="E467">
-        <f t="shared" si="7"/>
-        <v>10.771073200000004</v>
+        <v>38.552949999999989</v>
       </c>
     </row>
     <row r="468" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A468" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="B468">
         <v>22.751999999999999</v>
@@ -10340,13 +9884,12 @@
         <v>2623571.1835000012</v>
       </c>
       <c r="E468">
-        <f t="shared" si="7"/>
-        <v>26.235711835000011</v>
+        <v>125.94000000000001</v>
       </c>
     </row>
     <row r="469" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A469" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="B469">
         <v>23.177</v>
@@ -10358,13 +9901,12 @@
         <v>3055036.0365000018</v>
       </c>
       <c r="E469">
-        <f t="shared" si="7"/>
-        <v>30.550360365000017</v>
+        <v>124.82256730999998</v>
       </c>
     </row>
     <row r="470" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A470" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="B470">
         <v>21.241</v>
@@ -10376,13 +9918,12 @@
         <v>2608736.8030000012</v>
       </c>
       <c r="E470">
-        <f t="shared" si="7"/>
-        <v>26.087368030000011</v>
+        <v>123.36434</v>
       </c>
     </row>
     <row r="471" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A471" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="B471">
         <v>21.259</v>
@@ -10394,13 +9935,12 @@
         <v>3350672.5145000019</v>
       </c>
       <c r="E471">
-        <f t="shared" si="7"/>
-        <v>33.506725145000019</v>
+        <v>173.58828000000003</v>
       </c>
     </row>
     <row r="472" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A472" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="B472">
         <v>22.693999999999999</v>
@@ -10412,13 +9952,12 @@
         <v>2731275.2950000018</v>
       </c>
       <c r="E472">
-        <f t="shared" si="7"/>
-        <v>27.312752950000018</v>
+        <v>131.28460999999999</v>
       </c>
     </row>
     <row r="473" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A473" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="B473">
         <v>23.236000000000001</v>
@@ -10430,13 +9969,12 @@
         <v>2036445.6415000006</v>
       </c>
       <c r="E473">
-        <f t="shared" si="7"/>
-        <v>20.364456415000006</v>
+        <v>98.051217180000023</v>
       </c>
     </row>
     <row r="474" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A474" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="B474">
         <v>23.164000000000001</v>
@@ -10448,13 +9986,12 @@
         <v>3621469.2050000001</v>
       </c>
       <c r="E474">
-        <f t="shared" si="7"/>
-        <v>36.214692050000004</v>
+        <v>156.22850862000001</v>
       </c>
     </row>
     <row r="475" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A475" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="B475">
         <v>22.724</v>
@@ -10466,13 +10003,12 @@
         <v>1985922.4195000012</v>
       </c>
       <c r="E475">
-        <f t="shared" si="7"/>
-        <v>19.859224195000014</v>
+        <v>108.78155000000001</v>
       </c>
     </row>
     <row r="476" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A476" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="B476">
         <v>23.186</v>
@@ -10484,13 +10020,12 @@
         <v>2817383.850000001</v>
       </c>
       <c r="E476">
-        <f t="shared" si="7"/>
-        <v>28.173838500000009</v>
+        <v>147.33710398000002</v>
       </c>
     </row>
     <row r="477" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A477" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="B477">
         <v>23.251000000000001</v>
@@ -10502,13 +10037,12 @@
         <v>3770279.7585000023</v>
       </c>
       <c r="E477">
-        <f t="shared" si="7"/>
-        <v>37.70279758500002</v>
+        <v>191.04121999999998</v>
       </c>
     </row>
     <row r="478" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A478" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="B478">
         <v>21.216999999999999</v>
@@ -10520,13 +10054,12 @@
         <v>2691775.6850000015</v>
       </c>
       <c r="E478">
-        <f t="shared" si="7"/>
-        <v>26.917756850000014</v>
+        <v>115.35392000000002</v>
       </c>
     </row>
     <row r="479" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A479" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="B479">
         <v>23.193000000000001</v>
@@ -10538,13 +10071,12 @@
         <v>2738998.049000001</v>
       </c>
       <c r="E479">
-        <f t="shared" si="7"/>
-        <v>27.38998049000001</v>
+        <v>125.61113999999999</v>
       </c>
     </row>
     <row r="480" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A480" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="B480">
         <v>22.652000000000001</v>
@@ -10556,13 +10088,12 @@
         <v>2409181.4290000014</v>
       </c>
       <c r="E480">
-        <f t="shared" si="7"/>
-        <v>24.091814290000013</v>
+        <v>142.23318404</v>
       </c>
     </row>
     <row r="481" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A481" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="B481">
         <v>22.962</v>
@@ -10574,13 +10105,12 @@
         <v>1999649.923</v>
       </c>
       <c r="E481">
-        <f t="shared" si="7"/>
-        <v>19.996499230000001</v>
+        <v>90.834789970000017</v>
       </c>
     </row>
     <row r="482" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A482" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="B482">
         <v>23.817</v>
@@ -10592,13 +10122,12 @@
         <v>2980331.4154999997</v>
       </c>
       <c r="E482">
-        <f t="shared" si="7"/>
-        <v>29.803314154999995</v>
+        <v>133.14993041000002</v>
       </c>
     </row>
     <row r="483" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A483" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="B483">
         <v>21.818000000000001</v>
@@ -10610,13 +10139,12 @@
         <v>2758237.7455000011</v>
       </c>
       <c r="E483">
-        <f t="shared" si="7"/>
-        <v>27.58237745500001</v>
+        <v>127.76053999999999</v>
       </c>
     </row>
     <row r="484" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A484" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="B484">
         <v>23.303999999999998</v>
@@ -10628,13 +10156,12 @@
         <v>2246760.4955000007</v>
       </c>
       <c r="E484">
-        <f t="shared" si="7"/>
-        <v>22.467604955000006</v>
+        <v>109.79968</v>
       </c>
     </row>
     <row r="485" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A485" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="B485">
         <v>23.841000000000001</v>
@@ -10646,13 +10173,12 @@
         <v>2429311.9565000003</v>
       </c>
       <c r="E485">
-        <f t="shared" si="7"/>
-        <v>24.293119565000005</v>
+        <v>131.96288887</v>
       </c>
     </row>
     <row r="486" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A486" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="B486">
         <v>24.545000000000002</v>
@@ -10664,13 +10190,12 @@
         <v>3362983.0788000012</v>
       </c>
       <c r="E486">
-        <f t="shared" si="7"/>
-        <v>33.629830788000014</v>
+        <v>175.20770010000001</v>
       </c>
     </row>
     <row r="487" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A487" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="B487">
         <v>21.895</v>
@@ -10682,13 +10207,12 @@
         <v>3326372.5360000012</v>
       </c>
       <c r="E487">
-        <f t="shared" si="7"/>
-        <v>33.263725360000009</v>
+        <v>168.87163999999996</v>
       </c>
     </row>
     <row r="488" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A488" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="B488">
         <v>19.167000000000002</v>
@@ -10700,13 +10224,12 @@
         <v>1905680.4029000008</v>
       </c>
       <c r="E488">
-        <f t="shared" si="7"/>
-        <v>19.056804029000009</v>
+        <v>66.756649999999993</v>
       </c>
     </row>
     <row r="489" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A489" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="B489">
         <v>23.231999999999999</v>
@@ -10718,13 +10241,12 @@
         <v>1987915.0050000008</v>
       </c>
       <c r="E489">
-        <f t="shared" si="7"/>
-        <v>19.879150050000007</v>
+        <v>126.85732685999999</v>
       </c>
     </row>
     <row r="490" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A490" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="B490">
         <v>22.76</v>
@@ -10736,13 +10258,12 @@
         <v>2523601.6940000011</v>
       </c>
       <c r="E490">
-        <f t="shared" si="7"/>
-        <v>25.23601694000001</v>
+        <v>115.03028</v>
       </c>
     </row>
     <row r="491" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A491" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="B491">
         <v>19.151</v>
@@ -10754,13 +10275,12 @@
         <v>2238605.415000001</v>
       </c>
       <c r="E491">
-        <f t="shared" si="7"/>
-        <v>22.38605415000001</v>
+        <v>89.62715</v>
       </c>
     </row>
     <row r="492" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A492" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="B492">
         <v>21.215</v>
@@ -10772,13 +10292,12 @@
         <v>1037505.4415000001</v>
       </c>
       <c r="E492">
-        <f t="shared" si="7"/>
-        <v>10.375054415000001</v>
+        <v>43.78264999999999</v>
       </c>
     </row>
     <row r="493" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A493" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="B493">
         <v>23.207999999999998</v>
@@ -10790,13 +10309,12 @@
         <v>1193390.5225000002</v>
       </c>
       <c r="E493">
-        <f t="shared" si="7"/>
-        <v>11.933905225000002</v>
+        <v>60.093299999999999</v>
       </c>
     </row>
     <row r="494" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A494" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="B494">
         <v>23.846</v>
@@ -10808,13 +10326,12 @@
         <v>1680634.2675000001</v>
       </c>
       <c r="E494">
-        <f t="shared" si="7"/>
-        <v>16.806342675</v>
+        <v>76.391649230000013</v>
       </c>
     </row>
     <row r="495" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A495" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="B495">
         <v>23.215</v>
@@ -10826,13 +10343,12 @@
         <v>1121915.0150000004</v>
       </c>
       <c r="E495">
-        <f t="shared" si="7"/>
-        <v>11.219150150000004</v>
+        <v>54.111926679999996</v>
       </c>
     </row>
     <row r="496" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A496" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="B496">
         <v>20.532</v>
@@ -10844,13 +10360,12 @@
         <v>1450741.6500000004</v>
       </c>
       <c r="E496">
-        <f t="shared" si="7"/>
-        <v>14.507416500000003</v>
+        <v>59.606800000000007</v>
       </c>
     </row>
     <row r="497" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A497" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="B497">
         <v>20.704999999999998</v>
@@ -10862,13 +10377,12 @@
         <v>1271516.1200000003</v>
       </c>
       <c r="E497">
-        <f t="shared" si="7"/>
-        <v>12.715161200000004</v>
+        <v>61.338650000000001</v>
       </c>
     </row>
     <row r="498" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A498" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="B498">
         <v>23.338999999999999</v>
@@ -10880,13 +10394,12 @@
         <v>1946250.8500000013</v>
       </c>
       <c r="E498">
-        <f t="shared" si="7"/>
-        <v>19.462508500000013</v>
+        <v>64.458882060000008</v>
       </c>
     </row>
     <row r="499" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A499" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="B499">
         <v>23.454999999999998</v>
@@ -10898,13 +10411,12 @@
         <v>1299609.4900000002</v>
       </c>
       <c r="E499">
-        <f t="shared" si="7"/>
-        <v>12.996094900000003</v>
+        <v>63.661797930000006</v>
       </c>
     </row>
     <row r="500" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A500" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="B500">
         <v>22.064</v>
@@ -10916,13 +10428,12 @@
         <v>1642734.55</v>
       </c>
       <c r="E500">
-        <f t="shared" si="7"/>
-        <v>16.427345500000001</v>
+        <v>97.11096000000002</v>
       </c>
     </row>
     <row r="501" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A501" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="B501">
         <v>22.09</v>
@@ -10934,13 +10445,12 @@
         <v>1551189.41</v>
       </c>
       <c r="E501">
-        <f t="shared" si="7"/>
-        <v>15.511894099999999</v>
+        <v>77.126550000000009</v>
       </c>
     </row>
     <row r="502" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A502" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="B502">
         <v>22.529</v>
@@ -10952,13 +10462,12 @@
         <v>1214165.6235000002</v>
       </c>
       <c r="E502">
-        <f t="shared" si="7"/>
-        <v>12.141656235000003</v>
+        <v>63.695439999999991</v>
       </c>
     </row>
     <row r="503" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A503" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="B503">
         <v>22.071999999999999</v>
@@ -10970,13 +10479,12 @@
         <v>848792.54000000039</v>
       </c>
       <c r="E503">
-        <f t="shared" si="7"/>
-        <v>8.4879254000000035</v>
+        <v>39.405450000000002</v>
       </c>
     </row>
     <row r="504" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A504" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="B504">
         <v>21.74</v>
@@ -10988,13 +10496,12 @@
         <v>1843681.1799999997</v>
       </c>
       <c r="E504">
-        <f t="shared" si="7"/>
-        <v>18.436811799999997</v>
+        <v>51.328119999999998</v>
       </c>
     </row>
     <row r="505" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A505" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="B505">
         <v>22.606000000000002</v>
@@ -11006,8 +10513,7 @@
         <v>1209168.4800000002</v>
       </c>
       <c r="E505">
-        <f t="shared" si="7"/>
-        <v>12.091684800000003</v>
+        <v>48.435919999999996</v>
       </c>
     </row>
   </sheetData>

--- a/saavu2.xlsx
+++ b/saavu2.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/84c9e8aa81d5b49a/Desktop/weighted-kmeans-dc-location/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/84c9e8aa81d5b49a/Desktop/Supplychain-DC/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{B277FC28-4745-4223-8C79-53AD42E5289A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C9EB9C72-DFBB-4E87-BF8E-0C2A3DA7B62E}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{1EDEFCC3-5858-4EEB-B772-77B8F6028255}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{380CBB52-7125-4A1B-B64D-4699DB8CB28D}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6C2950A3-A5DC-4E1C-8EC9-030D30FBD1A4}"/>
   </bookViews>
@@ -1560,7 +1560,7 @@
     <t>long</t>
   </si>
   <si>
-    <t>demand_cft</t>
+    <t>order demand ( in cft)</t>
   </si>
 </sst>
 </file>
@@ -1626,6 +1626,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1928,7 +1932,7 @@
   <dimension ref="A1:E505"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="5" max="5" width="16.109375" customWidth="1"/>
+    <col min="5" max="5" width="14.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
@@ -2010,7 +2014,7 @@
         <v>80.004999999999995</v>
       </c>
       <c r="D5">
-        <v>10000</v>
+        <v>2819658</v>
       </c>
       <c r="E5">
         <v>93.988592240000003</v>
@@ -2910,7 +2914,7 @@
       <c r="C58">
         <v>73.867999999999995</v>
       </c>
-      <c r="D58">
+      <c r="D58" s="2">
         <v>1227601.5199999998</v>
       </c>
       <c r="E58" s="2">
@@ -3131,7 +3135,7 @@
       <c r="C71">
         <v>73.867999999999995</v>
       </c>
-      <c r="D71">
+      <c r="D71" s="2">
         <v>214758.73</v>
       </c>
       <c r="E71" s="2">
@@ -6450,7 +6454,7 @@
         <v>1194645.2550000001</v>
       </c>
       <c r="E266">
-        <v>995.34720000000016</v>
+        <v>980</v>
       </c>
     </row>
     <row r="267" spans="1:5" x14ac:dyDescent="0.3">
@@ -8282,7 +8286,7 @@
       <c r="C374">
         <v>74.945999999999998</v>
       </c>
-      <c r="D374">
+      <c r="D374" s="2">
         <v>3390955.100000001</v>
       </c>
       <c r="E374" s="2">

--- a/saavu2.xlsx
+++ b/saavu2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/84c9e8aa81d5b49a/Desktop/Supplychain-DC/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{1EDEFCC3-5858-4EEB-B772-77B8F6028255}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{380CBB52-7125-4A1B-B64D-4699DB8CB28D}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="13_ncr:1_{1EDEFCC3-5858-4EEB-B772-77B8F6028255}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3C778B2C-570A-4B40-B020-5FD0903684FE}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6C2950A3-A5DC-4E1C-8EC9-030D30FBD1A4}"/>
   </bookViews>
@@ -1560,7 +1560,7 @@
     <t>long</t>
   </si>
   <si>
-    <t>order demand ( in cft)</t>
+    <t>demand_cft</t>
   </si>
 </sst>
 </file>

--- a/saavu2.xlsx
+++ b/saavu2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/84c9e8aa81d5b49a/Desktop/Supplychain-DC/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="13_ncr:1_{1EDEFCC3-5858-4EEB-B772-77B8F6028255}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3C778B2C-570A-4B40-B020-5FD0903684FE}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="13_ncr:1_{1EDEFCC3-5858-4EEB-B772-77B8F6028255}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{29F2D223-79D7-49F8-B159-7FC2E6EEA274}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6C2950A3-A5DC-4E1C-8EC9-030D30FBD1A4}"/>
   </bookViews>
@@ -6266,8 +6266,9 @@
       <c r="D255">
         <v>1069336.4900000002</v>
       </c>
-      <c r="E255">
-        <v>898.03800000000024</v>
+      <c r="E255" s="2">
+        <f>898.038/4.5</f>
+        <v>199.56399999999999</v>
       </c>
     </row>
     <row r="256" spans="1:5" x14ac:dyDescent="0.3">
@@ -6334,8 +6335,9 @@
       <c r="D259">
         <v>2434991.2800000007</v>
       </c>
-      <c r="E259">
-        <v>571.54199999999992</v>
+      <c r="E259" s="2">
+        <f>571.542/2</f>
+        <v>285.77100000000002</v>
       </c>
     </row>
     <row r="260" spans="1:5" x14ac:dyDescent="0.3">
@@ -6453,8 +6455,9 @@
       <c r="D266">
         <v>1194645.2550000001</v>
       </c>
-      <c r="E266">
-        <v>980</v>
+      <c r="E266" s="2">
+        <f>995.3472/4</f>
+        <v>248.83680000000001</v>
       </c>
     </row>
     <row r="267" spans="1:5" x14ac:dyDescent="0.3">
